--- a/セリフ編集/キャラタイプ別/丁寧×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×お気楽.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:H210"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="F74" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">引き分けですって。ちょうどいいじゃないですか。</t>
+          <t xml:space="preserve">決着つかずですって。ちょうどいいじゃないですか。</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.easygoing.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETAIN_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.easygoing.polite[1]</t>
+          <t xml:space="preserve">accepted.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="F83" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残ります！ まだまだここで頑張りたいです！</t>
+          <t xml:space="preserve">お世話になりました〜！ また、どこかでお会いできたら嬉しいです！</t>
         </is>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.easygoing.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.easygoing.polite[1]</t>
+          <t xml:space="preserve">accepted.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3013,14 +3013,14 @@
       </c>
       <c r="F84" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わかりました。…楽しかったです。本当に</t>
+          <t xml:space="preserve">行ってきます〜！</t>
         </is>
       </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.easygoing.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.easygoing.polite[1]</t>
+          <t xml:space="preserve">defended.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3045,14 +3045,14 @@
       </c>
       <c r="F85" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まだです！ まだやれます！ もう少しだけお願いします！</t>
+          <t xml:space="preserve">えへへ、引き留めてくださって嬉しいです！</t>
         </is>
       </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.easygoing.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.easygoing.polite[1]</t>
+          <t xml:space="preserve">defended.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3077,14 +3077,14 @@
       </c>
       <c r="F86" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">正直、もう限界だと感じています。…引退を考えています</t>
+          <t xml:space="preserve">残ります〜！ これからもよろしくお願いします〜</t>
         </is>
       </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">defense_failed.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3109,14 +3109,14 @@
       </c>
       <c r="F87" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残らせていただきますね!ここ、すごく楽しいんです!</t>
+          <t xml:space="preserve">ごめんなさい〜、引き留めていただいたのに…！</t>
         </is>
       </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.easygoing.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3126,29 +3126,29 @@
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES</t>
         </is>
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.easygoing.polite[1]</t>
+          <t xml:space="preserve">defense_failed.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F88" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます！ 前向きに考えます！</t>
+          <t xml:space="preserve">…お元気で〜！</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3158,29 +3158,29 @@
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">RETAIN_LINES</t>
         </is>
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.easygoing.polite[1]</t>
+          <t xml:space="preserve">former_champ.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">06 契約交渉</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F89" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">条件次第ですね。…聞かせてください！</t>
+          <t xml:space="preserve">残ります！ まだまだここで頑張りたいです！</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3190,29 +3190,29 @@
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES</t>
         </is>
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">accept_terminal.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F90" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか最近調子いいんです！ もっと上に行けそうです！</t>
+          <t xml:space="preserve">わかりました。…楽しかったです。本当に</t>
         </is>
       </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3222,29 +3222,29 @@
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES</t>
         </is>
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">refuse_champ.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F91" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近ちょっとモチベーションが…でも頑張ります</t>
+          <t xml:space="preserve">まだです！ まだやれます！ もう少しだけお願いします！</t>
         </is>
       </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3254,29 +3254,29 @@
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">A1_champion.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F92" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やる気出てきました！ もう大丈夫です！</t>
+          <t xml:space="preserve">正直、もう限界だと感じています。…引退を考えています</t>
         </is>
       </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3286,29 +3286,29 @@
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">A2_uncrowned.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F93" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子戻ってきました！ もう大丈夫です！</t>
+          <t xml:space="preserve">ベルトは無理でしたけど…楽しかったです、本当に</t>
         </is>
       </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3318,29 +3318,29 @@
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.easygoing.polite[1]</t>
+          <t xml:space="preserve">A3_heel.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F94" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近ちょっと調子悪くて…でも大丈夫です！</t>
+          <t xml:space="preserve">最後くらい、素直になってもいいですか。楽しかったです</t>
         </is>
       </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3350,29 +3350,29 @@
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.easygoing.polite[1]</t>
+          <t xml:space="preserve">A4_veteran.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F95" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合でした！ 相手にも感謝です！</t>
+          <t xml:space="preserve">いやあ、長かったです。でも、あっという間でしたね</t>
         </is>
       </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3382,29 +3382,29 @@
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.polite[1]</t>
+          <t xml:space="preserve">B1_young.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F96" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間守り抜きました！ 来年も頑張ります！</t>
+          <t xml:space="preserve">え…うそ…まだ、これからだったんですけど…</t>
         </is>
       </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3414,29 +3414,29 @@
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.easygoing.polite[1]</t>
+          <t xml:space="preserve">B2_prime.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F97" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入りですか…！ 信じられません…ありがとうございます！</t>
+          <t xml:space="preserve">あはは…参りました。これからだったのに…</t>
         </is>
       </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3446,29 +3446,29 @@
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.easygoing.polite[1]</t>
+          <t xml:space="preserve">B3_older.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F98" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPですか！ ありがとうございます！ 来年も頑張ります！</t>
+          <t xml:space="preserve">まあ、十分やりましたよね。いい人生でした</t>
         </is>
       </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3478,29 +3478,29 @@
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">RETIREMENT_LINES</t>
         </is>
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.easygoing.polite[1]</t>
+          <t xml:space="preserve">B4_champion_injury.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F99" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うそです…！ 新人王ですか…！ ありがとうございます！</t>
+          <t xml:space="preserve">あちゃー…ベルトを持ったまま終わりですか…</t>
         </is>
       </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES</t>
         </is>
       </c>
       <c r="D100" t="inlineStr" s="12">
@@ -3520,19 +3520,19 @@
       </c>
       <c r="E100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">05 引退・引き抜き・引き留め</t>
         </is>
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム、嬉しいですね。気負わずいきましょう</t>
+          <t xml:space="preserve">残らせていただきますね!ここ、すごく楽しいんです!</t>
         </is>
       </c>
     </row>
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3542,29 +3542,29 @@
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">raise_accept.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様と一緒に楽しい時間を作れたら</t>
+          <t xml:space="preserve">わあ、ありがとうございます！ さすが社長です！ 今年も楽しくやらせてくださいね！</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.polite[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3574,29 +3574,29 @@
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[3]</t>
+          <t xml:space="preserve">raise_negotiate_accept.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ゆったり構えて、精一杯やります</t>
+          <t xml:space="preserve">んー、まあいいです！ いただけるだけありがたいということで！</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3606,29 +3606,29 @@
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員、嬉しいですね。本当に感謝です</t>
+          <t xml:space="preserve">あちゃー、だめですかー。まあ仕方ないですよね。……ちょっとへこみますけど。</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3638,29 +3638,29 @@
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">raise_open.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みなさんが来てくれたおかげですね</t>
+          <t xml:space="preserve">ありがとうございます！ 前向きに考えます！</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.polite[3]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3670,29 +3670,29 @@
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[3]</t>
+          <t xml:space="preserve">raise_refuse.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ゆったりと喜びを噛みしめます</t>
+          <t xml:space="preserve">あはは、やっぱりですかー。まあ仕方ないですね。でもいつか上げてくださいね？ 約束ですよ？</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3702,29 +3702,29 @@
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.easygoing.polite[1]</t>
+          <t xml:space="preserve">transfer_listen.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったー!信じられない、夢みたい……!</t>
+          <t xml:space="preserve">聞いてくださるんですか？ うーん……{record}なんだかマンネリっていうか。新しいことがしたいんです。</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3734,29 +3734,29 @@
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">transfer_open.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いしますね〜 楽しみです</t>
+          <t xml:space="preserve">社長、あのですね。{tenure}いろいろ考えたのですが……環境を変えてみたいなと思いまして。</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3766,29 +3766,29 @@
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">transfer_open.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、ちょっと休みますね〜 すぐ戻ります</t>
+          <t xml:space="preserve">いやー社長、言いにくいのですが。{tenure}少し外の空気を吸ってみたいんです。</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3798,29 +3798,29 @@
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.easygoing.polite[1]</t>
+          <t xml:space="preserve">transfer_release.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いしますね〜 楽しみです</t>
+          <t xml:space="preserve">あはは、まあそうなりますよねー。{tenure_farewell}{rivalry}お元気でー！</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3830,29 +3830,29 @@
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.easygoing.polite[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、ちょっと休みますね〜 すぐ戻ります</t>
+          <t xml:space="preserve">ごめんなさい社長……。お金の問題じゃないんです。もう心が決まってしまって。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3862,29 +3862,29 @@
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.easygoing.polite[1]</t>
+          <t xml:space="preserve">transfer_retain_success.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、ご縁がなかったですね〜 ありがとうございました</t>
+          <t xml:space="preserve">え、本当ですか？ そこまでしてくださるんですか？ ……じゃあ、もう少しいようかな！</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3894,29 +3894,29 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">start.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、ご縁がなかったですね〜 ありがとうございました</t>
+          <t xml:space="preserve">条件次第ですね。…聞かせてください！</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3926,29 +3926,29 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気楽にお付き合いできて嬉しいです〜</t>
+          <t xml:space="preserve">なんか最近調子いいんです！ もっと上に行けそうです！</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
@@ -3968,19 +3968,19 @@
       </c>
       <c r="E114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝ストップかあ…でもまた頑張ります！</t>
+          <t xml:space="preserve">最近ちょっとモチベーションが…でも頑張ります</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3990,29 +3990,29 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.polite[1]</t>
+          <t xml:space="preserve">easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、身体はもうへとへとです。でも、最後まで頑張りますよ</t>
+          <t xml:space="preserve">やる気出てきました！ もう大丈夫です！</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.polite[2]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4022,29 +4022,29 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.polite[2]</t>
+          <t xml:space="preserve">easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たら、やるしかないですよね。痛いけど、まあいっか</t>
+          <t xml:space="preserve">調子戻ってきました！ もう大丈夫です！</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.polite[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4054,29 +4054,29 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.polite[1]</t>
+          <t xml:space="preserve">defeat.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手の方ですね。えーと、気楽に…いや、ちゃんとやります</t>
+          <t xml:space="preserve">最近ちょっと調子悪くて…でも大丈夫です！</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.polite[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4086,29 +4086,29 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.polite[2]</t>
+          <t xml:space="preserve">bestMatch.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつ、しっかりお相手しますよ。ま、任せてください</t>
+          <t xml:space="preserve">最高の試合でした！ 相手にも感謝です！</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4118,29 +4118,29 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.polite[1]</t>
+          <t xml:space="preserve">champion.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、倒せました。…はぁ、疲れましたけど、まだ退けません。次の方、どうぞ</t>
+          <t xml:space="preserve">一年間守り抜きました！ 来年も頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.polite[2]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.polite[2]</t>
+          <t xml:space="preserve">hallOfFame.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふう、一人おしまいです。でも、まだ立ってますよ。次、来てくださいねー</t>
+          <t xml:space="preserve">殿堂入りですか…！ 信じられません…ありがとうございます！</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4182,29 +4182,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.polite[1]</t>
+          <t xml:space="preserve">mvp.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高のチームでしたよね。三人で勝てて、本当に嬉しいです</t>
+          <t xml:space="preserve">MVPですか！ ありがとうございます！ 来年も頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.polite[2]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4214,29 +4214,29 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.polite[2]</t>
+          <t xml:space="preserve">rookie.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間がいてくれたから、のびのびやれました。ありがとうございます</t>
+          <t xml:space="preserve">うそです…！ 新人王ですか…！ ありがとうございます！</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4246,29 +4246,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.polite[1]</t>
+          <t xml:space="preserve">easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPはありがたいですけど……やっぱり、みんなで勝ちたかったですね</t>
+          <t xml:space="preserve">ドーム、嬉しいですね。気負わずいきましょう</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.polite[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4278,29 +4278,29 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.polite[2]</t>
+          <t xml:space="preserve">easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は三人揃って笑えるように。そう思ってます</t>
+          <t xml:space="preserve">お客様と一緒に楽しい時間を作れたら</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.polite[3]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4310,29 +4310,29 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.polite[1]</t>
+          <t xml:space="preserve">easygoing.polite[3]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、何人来たか覚えてないです。でも、全部楽しかったですよ</t>
+          <t xml:space="preserve">ゆったり構えて、精一杯やります</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.polite[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4342,29 +4342,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.polite[2]</t>
+          <t xml:space="preserve">easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足がふらふらしてますけど……全員倒したから、まあいっかって感じです</t>
+          <t xml:space="preserve">満員、嬉しいですね。本当に感謝です</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4374,29 +4374,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で行きます！ よろしくお願いします！</t>
+          <t xml:space="preserve">みなさんが来てくれたおかげですね</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.polite[3]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4406,29 +4406,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">easygoing.polite[3]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった、勝ちました!最高の舞台で最高の結果、夢みたいです!</t>
+          <t xml:space="preserve">ゆったりと喜びを噛みしめます</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4438,59 +4438,2619 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">E1.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました！ うちの団体の底力を見せられましたね！</t>
+          <t xml:space="preserve">もっと多くの方に見ていただきたくて…出させていただけませんか</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">E1.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">テレビ、ですか…！ぜひ、出させてください！</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="40" customHeight="1">
+      <c r="A131" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">E1.accept.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やったー!信じられない、夢みたい……!</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="40" customHeight="1">
+      <c r="A132" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">えへへ、一緒に楽しくやりましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="40" customHeight="1">
+      <c r="A133" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">退屈なプロレスはしないって約束します</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="40" customHeight="1">
+      <c r="A134" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よろしくお願いしますね〜 楽しみです</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="40" customHeight="1">
+      <c r="A135" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やっほー、新天地です！暴れまくりますよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="40" customHeight="1">
+      <c r="A136" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここなら好き放題やれそうです。楽しみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="40" customHeight="1">
+      <c r="A137" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わーい、今日から仲間です！よろしくお願いします</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="40" customHeight="1">
+      <c r="A138" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">みんなで楽しくやりましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="40" customHeight="1">
+      <c r="A139" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、ちょっと休みますね〜 すぐ戻ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="40" customHeight="1">
+      <c r="A140" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">draftInterest.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">えへへ、一緒に楽しくやりましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="40" customHeight="1">
+      <c r="A141" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">draftInterest.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">退屈なプロレスはしないって約束します</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="40" customHeight="1">
+      <c r="A142" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">draftJoin.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">よろしくお願いしますね〜 楽しみです</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="40" customHeight="1">
+      <c r="A143" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faGreeting.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">フリー生活、今日で終わりです！助かりました</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="40" customHeight="1">
+      <c r="A144" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faSigning.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やっほー、新天地です！暴れまくりますよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="40" customHeight="1">
+      <c r="A145" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faSigning.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここなら好き放題やれそうです。楽しみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="40" customHeight="1">
+      <c r="A146" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faWelcome.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">わーい、今日から仲間です！よろしくお願いします</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="40" customHeight="1">
+      <c r="A147" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">faWelcome.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">みんなで楽しくやりましょう</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="40" customHeight="1">
+      <c r="A148" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">injury.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あ、ちょっと休みますね〜 すぐ戻ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="40" customHeight="1">
+      <c r="A149" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">release.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あはは、ご縁がなかったですね〜 ありがとうございました</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="40" customHeight="1">
+      <c r="A150" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rentalGreeting.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">おじゃましまーす！短い間ですけど暴れますよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="40" customHeight="1">
+      <c r="A151" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rentalGreeting.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一時的だからこそ、思い切り好き放題やりますね</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="40" customHeight="1">
+      <c r="A152" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">scoutGreeting.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">見つけてくださって助かりました！暴れますね</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="40" customHeight="1">
+      <c r="A153" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleChallengeLoss.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日は負けちゃいましたけど…次はもっといい試合をします</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="40" customHeight="1">
+      <c r="A154" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleChallengeLoss.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">悔しいですけど、下を向いてたら応援してくれる人に失礼ですもんね</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="40" customHeight="1">
+      <c r="A155" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleDefense.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">チャンピオンはわたしです。また守り切りました</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="40" customHeight="1">
+      <c r="A156" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleDefense.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい試合でした。また挑戦してきてくださいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="40" customHeight="1">
+      <c r="A157" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleLoss.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けちゃいました…でもファンが応援してくれる限り、立ち上がります</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="40" customHeight="1">
+      <c r="A158" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleLoss.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ベルトのない自分なんて想像できませんでした。でも、わたしはわたしですから</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="40" customHeight="1">
+      <c r="A159" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleWin.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">新チャンピオン誕生です。これからもっと盛り上げます</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="40" customHeight="1">
+      <c r="A160" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">titleWin.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ベルト獲っちゃいました。最高です</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="40" customHeight="1">
+      <c r="A161" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あはは、ご縁がなかったですね〜 ありがとうございました</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="40" customHeight="1">
+      <c r="A162" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">おじゃましまーす！短い間ですけど暴れますよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="40" customHeight="1">
+      <c r="A163" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一時的だからこそ、思い切り好き放題やりますね</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="40" customHeight="1">
+      <c r="A164" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">今日は負けちゃいましたけど…次はもっといい試合をします</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="40" customHeight="1">
+      <c r="A165" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">悔しいですけど、下を向いてたら応援してくれる人に失礼ですもんね</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="40" customHeight="1">
+      <c r="A166" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">チャンピオンはわたしです。また守り切りました</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="40" customHeight="1">
+      <c r="A167" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい試合でした。また挑戦してきてくださいね</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="40" customHeight="1">
+      <c r="A168" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">負けちゃいました…でもファンが応援してくれる限り、立ち上がります</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="40" customHeight="1">
+      <c r="A169" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ベルトのない自分なんて想像できませんでした。でも、わたしはわたしですから</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="40" customHeight="1">
+      <c r="A170" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">新チャンピオン誕生です。これからもっと盛り上げます</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="40" customHeight="1">
+      <c r="A171" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ベルト獲っちゃいました。最高です</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="40" customHeight="1">
+      <c r="A172" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_39_down.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">う〜ん、ちょっと合わないかもしれません…</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="40" customHeight="1">
+      <c r="A173" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あれ〜、最近ちょっと素っ気ないような…</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="40" customHeight="1">
+      <c r="A174" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ん〜、なんだか少し空気が変わりましたかね〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="40" customHeight="1">
+      <c r="A175" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_60_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">気楽にお付き合いできて嬉しいです〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="40" customHeight="1">
+      <c r="A176" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高の相棒です〜。ずっと一緒にいたいですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="40" customHeight="1">
+      <c r="A177" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一緒だと、何もかも上手くいく気がするんです</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="40" customHeight="1">
+      <c r="A178" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">熱い関係も一段落ですね。ちょっと寂しいです</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="40" customHeight="1">
+      <c r="A179" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まぁ因縁も永遠じゃありませんよね〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="40" customHeight="1">
+      <c r="A180" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい勝負になりそうですね〜。燃えてきました</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="40" customHeight="1">
+      <c r="A181" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あはは、負けたくないです〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="40" customHeight="1">
+      <c r="A182" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">本気でやり合いたい相手なんて、そういませんよ〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="40" customHeight="1">
+      <c r="A183" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふ、考えると自然と気合が入ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="40" customHeight="1">
+      <c r="A184" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この試合が一番楽しいんです。ずっとこの関係が続けばいいのに</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="40" customHeight="1">
+      <c r="A185" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">運命のライバルですね〜。最高です</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="40" customHeight="1">
+      <c r="A186" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここ最高です〜！ みんなとやるの楽しいです！</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="40" customHeight="1">
+      <c r="A187" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この団体、すっごく居心地いいんですよね〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="40" customHeight="1">
+      <c r="A188" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">さすがにこれは…笑えないですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="40" customHeight="1">
+      <c r="A189" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あはは…なんて笑っている場合じゃないですよね、これ</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="40" customHeight="1">
+      <c r="A190" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">う〜ん、最近ちょっとモヤモヤします…</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="40" customHeight="1">
+      <c r="A191" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まぁ大丈夫…ですよね？ ちょっと不安ですけど</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="40" customHeight="1">
+      <c r="A192" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">連勝ストップかあ…でもまた頑張ります！</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="40" customHeight="1">
+      <c r="A193" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あはは、身体はもうへとへとです。でも、最後まで頑張りますよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="40" customHeight="1">
+      <c r="A194" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来たら、やるしかないですよね。痛いけど、まあいっか</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="40" customHeight="1">
+      <c r="A195" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">相手の方ですね。えーと、気楽に…いや、ちゃんとやります</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="40" customHeight="1">
+      <c r="A196" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一戦ずつ、しっかりお相手しますよ。ま、任せてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="40" customHeight="1">
+      <c r="A197" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人、倒せました。…はぁ、疲れましたけど、まだ退けません。次の方、どうぞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="40" customHeight="1">
+      <c r="A198" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふう、一人おしまいです。でも、まだ立ってますよ。次、来てくださいねー</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="40" customHeight="1">
+      <c r="A199" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高のチームでしたよね。三人で勝てて、本当に嬉しいです</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="40" customHeight="1">
+      <c r="A200" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">仲間がいてくれたから、のびのびやれました。ありがとうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="40" customHeight="1">
+      <c r="A201" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">MVPはありがたいですけど……やっぱり、みんなで勝ちたかったですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="40" customHeight="1">
+      <c r="A202" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次は三人揃って笑えるように。そう思ってます</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="40" customHeight="1">
+      <c r="A203" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あはは、何人来たか覚えてないです。でも、全部楽しかったですよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="40" customHeight="1">
+      <c r="A204" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">足がふらふらしてますけど……全員倒したから、まあいっかって感じです</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="40" customHeight="1">
+      <c r="A205" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力で行きます！ よろしくお願いします！</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="40" customHeight="1">
+      <c r="A206" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やった、勝ちました!最高の舞台で最高の結果、夢みたいです!</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="40" customHeight="1">
+      <c r="A207" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちました！ うちの団体の底力を見せられましたね！</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="40" customHeight="1">
+      <c r="A208" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">ENDING_LINES.fighter.easygoing.polite[1]</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr" s="2">
+      <c r="B208" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ENDING_LINES</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr" s="12">
+      <c r="D208" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">fighter.easygoing.polite[1]</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr" s="2">
+      <c r="E208" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">18 経営危機・エンディング</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr" s="3">
+      <c r="F208" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">最後まで楽しかったです！ ありがとうございました！</t>
         </is>
       </c>
     </row>
+    <row r="209" ht="40" customHeight="1">
+      <c r="A209" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">フリー生活、今日で終わりです！助かりました</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="40" customHeight="1">
+      <c r="A210" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">見つけてくださって助かりました！暴れますね</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H130"/>
+  <autoFilter ref="A1:H210"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×お気楽.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H210"/>
+  <dimension ref="A1:H251"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -364,7 +364,7 @@
     <row r="2" ht="40" customHeight="1">
       <c r="A2" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.polite[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -379,7 +379,7 @@
       </c>
       <c r="D2" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.polite[1]</t>
+          <t xml:space="preserve">atk.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
@@ -396,7 +396,7 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.polite[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -411,7 +411,7 @@
       </c>
       <c r="D3" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.polite[2]</t>
+          <t xml:space="preserve">atk.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
@@ -428,7 +428,7 @@
     <row r="4" ht="40" customHeight="1">
       <c r="A4" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.polite[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.easygoing[3]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -443,7 +443,7 @@
       </c>
       <c r="D4" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.polite[3]</t>
+          <t xml:space="preserve">atk.polite.easygoing[3]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
@@ -460,7 +460,7 @@
     <row r="5" ht="40" customHeight="1">
       <c r="A5" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.atk.easygoing.polite[4]</t>
+          <t xml:space="preserve">CUTIN_LINES.atk.polite.easygoing[4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -475,7 +475,7 @@
       </c>
       <c r="D5" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">atk.easygoing.polite[4]</t>
+          <t xml:space="preserve">atk.polite.easygoing[4]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
@@ -492,7 +492,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="A6" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.polite[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
@@ -507,7 +507,7 @@
       </c>
       <c r="D6" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.polite[1]</t>
+          <t xml:space="preserve">bigmove.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
@@ -524,7 +524,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.polite[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
@@ -539,7 +539,7 @@
       </c>
       <c r="D7" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.polite[2]</t>
+          <t xml:space="preserve">bigmove.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
@@ -556,7 +556,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.bigmove.easygoing.polite[3]</t>
+          <t xml:space="preserve">CUTIN_LINES.bigmove.polite.easygoing[3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
@@ -571,7 +571,7 @@
       </c>
       <c r="D8" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bigmove.easygoing.polite[3]</t>
+          <t xml:space="preserve">bigmove.polite.easygoing[3]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
@@ -588,7 +588,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.easygoing.polite[1]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
@@ -603,7 +603,7 @@
       </c>
       <c r="D9" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.easygoing.polite[1]</t>
+          <t xml:space="preserve">climax.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
@@ -620,7 +620,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_LINES.climax.easygoing.polite[2]</t>
+          <t xml:space="preserve">CUTIN_LINES.climax.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
@@ -635,7 +635,7 @@
       </c>
       <c r="D10" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">climax.easygoing.polite[2]</t>
+          <t xml:space="preserve">climax.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
@@ -652,7 +652,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
@@ -667,7 +667,7 @@
       </c>
       <c r="D11" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
@@ -684,7 +684,7 @@
     <row r="12" ht="40" customHeight="1">
       <c r="A12" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
@@ -699,7 +699,7 @@
       </c>
       <c r="D12" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
@@ -716,7 +716,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DAMAGE_SERIF_LINES.easygoing.polite[3]</t>
+          <t xml:space="preserve">DAMAGE_SERIF_LINES.polite.easygoing[3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
@@ -731,7 +731,7 @@
       </c>
       <c r="D13" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[3]</t>
+          <t xml:space="preserve">polite.easygoing[3]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
@@ -748,7 +748,7 @@
     <row r="14" ht="40" customHeight="1">
       <c r="A14" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.easygoing.polite[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.badWinner.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
@@ -763,7 +763,7 @@
       </c>
       <c r="D14" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">badWinner.easygoing.polite[1]</t>
+          <t xml:space="preserve">badWinner.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
@@ -780,7 +780,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.easygoing.polite[1]</t>
+          <t xml:space="preserve">FAN_EXPECT_REACTIONS.goodWinner.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
@@ -795,7 +795,7 @@
       </c>
       <c r="D15" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">goodWinner.easygoing.polite[1]</t>
+          <t xml:space="preserve">goodWinner.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
@@ -812,7 +812,7 @@
     <row r="16" ht="40" customHeight="1">
       <c r="A16" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.easygoing.polite[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.competition_won.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
@@ -827,7 +827,7 @@
       </c>
       <c r="D16" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">competition_won.easygoing.polite[1]</t>
+          <t xml:space="preserve">competition_won.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
@@ -844,7 +844,7 @@
     <row r="17" ht="40" customHeight="1">
       <c r="A17" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.easygoing.polite[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.direct.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
@@ -859,7 +859,7 @@
       </c>
       <c r="D17" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">direct.easygoing.polite[1]</t>
+          <t xml:space="preserve">direct.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
@@ -876,7 +876,7 @@
     <row r="18" ht="40" customHeight="1">
       <c r="A18" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.easygoing.polite[1]</t>
+          <t xml:space="preserve">SCOUT_SIGNING_LINES.fa_signing.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
@@ -891,7 +891,7 @@
       </c>
       <c r="D18" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fa_signing.easygoing.polite[1]</t>
+          <t xml:space="preserve">fa_signing.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -908,7 +908,7 @@
     <row r="19" ht="40" customHeight="1">
       <c r="A19" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.polite.hit[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.easygoing.hit[1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
@@ -923,7 +923,7 @@
       </c>
       <c r="D19" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite.hit[1]</t>
+          <t xml:space="preserve">polite.easygoing.hit[1]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
@@ -940,7 +940,7 @@
     <row r="20" ht="40" customHeight="1">
       <c r="A20" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.polite.hit[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.easygoing.hit[2]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
@@ -955,7 +955,7 @@
       </c>
       <c r="D20" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite.hit[2]</t>
+          <t xml:space="preserve">polite.easygoing.hit[2]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
@@ -972,7 +972,7 @@
     <row r="21" ht="40" customHeight="1">
       <c r="A21" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.polite.win[1]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.easygoing.win[1]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
@@ -987,7 +987,7 @@
       </c>
       <c r="D21" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite.win[1]</t>
+          <t xml:space="preserve">polite.easygoing.win[1]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
@@ -1004,7 +1004,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.easygoing.polite.win[2]</t>
+          <t xml:space="preserve">VS_EX_EMPLOYER_LINES.polite.easygoing.win[2]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="D22" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite.win[2]</t>
+          <t xml:space="preserve">polite.easygoing.win[2]</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
@@ -1036,7 +1036,7 @@
     <row r="23" ht="40" customHeight="1">
       <c r="A23" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="D23" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr" s="2">
@@ -1068,7 +1068,7 @@
     <row r="24" ht="40" customHeight="1">
       <c r="A24" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D24" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr" s="2">
@@ -1100,7 +1100,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BETRAYAL_LINES.easygoing.polite[3]</t>
+          <t xml:space="preserve">BETRAYAL_LINES.polite.easygoing[3]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="D25" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[3]</t>
+          <t xml:space="preserve">polite.easygoing[3]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr" s="2">
@@ -1132,7 +1132,7 @@
     <row r="26" ht="40" customHeight="1">
       <c r="A26" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="D26" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E26" t="inlineStr" s="2">
@@ -1164,7 +1164,7 @@
     <row r="27" ht="40" customHeight="1">
       <c r="A27" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D27" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr" s="2">
@@ -1196,7 +1196,7 @@
     <row r="28" ht="40" customHeight="1">
       <c r="A28" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CUTIN_SAVE_LINES.easygoing.polite[3]</t>
+          <t xml:space="preserve">CUTIN_SAVE_LINES.polite.easygoing[3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="D28" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[3]</t>
+          <t xml:space="preserve">polite.easygoing[3]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr" s="2">
@@ -1228,7 +1228,7 @@
     <row r="29" ht="40" customHeight="1">
       <c r="A29" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D29" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr" s="2">
@@ -1260,7 +1260,7 @@
     <row r="30" ht="40" customHeight="1">
       <c r="A30" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="D30" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr" s="2">
@@ -1292,7 +1292,7 @@
     <row r="31" ht="40" customHeight="1">
       <c r="A31" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOUBLE_TEAM_LINES.easygoing.polite[3]</t>
+          <t xml:space="preserve">DOUBLE_TEAM_LINES.polite.easygoing[3]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="D31" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[3]</t>
+          <t xml:space="preserve">polite.easygoing[3]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr" s="2">
@@ -1324,7 +1324,7 @@
     <row r="32" ht="40" customHeight="1">
       <c r="A32" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D32" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr" s="2">
@@ -1356,7 +1356,7 @@
     <row r="33" ht="40" customHeight="1">
       <c r="A33" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="D33" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E33" t="inlineStr" s="2">
@@ -1388,7 +1388,7 @@
     <row r="34" ht="40" customHeight="1">
       <c r="A34" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">HOT_TAG_LINES.easygoing.polite[3]</t>
+          <t xml:space="preserve">HOT_TAG_LINES.polite.easygoing[3]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D34" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[3]</t>
+          <t xml:space="preserve">polite.easygoing[3]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr" s="2">
@@ -1420,7 +1420,7 @@
     <row r="35" ht="40" customHeight="1">
       <c r="A35" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="D35" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr" s="2">
@@ -1452,7 +1452,7 @@
     <row r="36" ht="40" customHeight="1">
       <c r="A36" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">TAG_MATCH_LOSS_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D36" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr" s="2">
@@ -1484,7 +1484,7 @@
     <row r="37" ht="40" customHeight="1">
       <c r="A37" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D37" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr" s="2">
@@ -1516,7 +1516,7 @@
     <row r="38" ht="40" customHeight="1">
       <c r="A38" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">TAG_MATCH_WIN_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">TAG_MATCH_WIN_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D38" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr" s="2">
@@ -1548,7 +1548,7 @@
     <row r="39" ht="40" customHeight="1">
       <c r="A39" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.easygoing.polite[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.loser.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="D39" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.polite[1]</t>
+          <t xml:space="preserve">loser.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr" s="2">
@@ -1580,7 +1580,7 @@
     <row r="40" ht="40" customHeight="1">
       <c r="A40" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.easygoing.polite[1]</t>
+          <t xml:space="preserve">BITTER_RESOLUTION_LINES.winner.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="D40" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.polite[1]</t>
+          <t xml:space="preserve">winner.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr" s="2">
@@ -1612,7 +1612,7 @@
     <row r="41" ht="40" customHeight="1">
       <c r="A41" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.easygoing.polite[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.loser.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D41" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.polite[1]</t>
+          <t xml:space="preserve">loser.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E41" t="inlineStr" s="2">
@@ -1644,7 +1644,7 @@
     <row r="42" ht="40" customHeight="1">
       <c r="A42" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.easygoing.polite[1]</t>
+          <t xml:space="preserve">GOODRIVAL_RESOLUTION_LINES.winner.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="D42" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.polite[1]</t>
+          <t xml:space="preserve">winner.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr" s="2">
@@ -1676,7 +1676,7 @@
     <row r="43" ht="40" customHeight="1">
       <c r="A43" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.easygoing.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.attacker.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="D43" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.polite[1]</t>
+          <t xml:space="preserve">attacker.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E43" t="inlineStr" s="2">
@@ -1708,7 +1708,7 @@
     <row r="44" ht="40" customHeight="1">
       <c r="A44" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.easygoing.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_70.defender.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="D44" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.polite[1]</t>
+          <t xml:space="preserve">defender.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E44" t="inlineStr" s="2">
@@ -1740,7 +1740,7 @@
     <row r="45" ht="40" customHeight="1">
       <c r="A45" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.easygoing.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.attacker.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="D45" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.polite[1]</t>
+          <t xml:space="preserve">attacker.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E45" t="inlineStr" s="2">
@@ -1772,7 +1772,7 @@
     <row r="46" ht="40" customHeight="1">
       <c r="A46" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.easygoing.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES_90.defender.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="D46" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.polite[1]</t>
+          <t xml:space="preserve">defender.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E46" t="inlineStr" s="2">
@@ -1804,7 +1804,7 @@
     <row r="47" ht="40" customHeight="1">
       <c r="A47" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.easygoing.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.attacker.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="D47" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">attacker.easygoing.polite[1]</t>
+          <t xml:space="preserve">attacker.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E47" t="inlineStr" s="2">
@@ -1836,7 +1836,7 @@
     <row r="48" ht="40" customHeight="1">
       <c r="A48" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.easygoing.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.defender.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="D48" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defender.easygoing.polite[1]</t>
+          <t xml:space="preserve">defender.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E48" t="inlineStr" s="2">
@@ -1868,7 +1868,7 @@
     <row r="49" ht="40" customHeight="1">
       <c r="A49" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.easygoing.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateAttacker.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="D49" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateAttacker.easygoing.polite[1]</t>
+          <t xml:space="preserve">fateAttacker.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E49" t="inlineStr" s="2">
@@ -1900,7 +1900,7 @@
     <row r="50" ht="40" customHeight="1">
       <c r="A50" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.easygoing.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_CONFRONTATION_LINES.fateDefender.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="D50" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateDefender.easygoing.polite[1]</t>
+          <t xml:space="preserve">fateDefender.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E50" t="inlineStr" s="2">
@@ -1932,7 +1932,7 @@
     <row r="51" ht="40" customHeight="1">
       <c r="A51" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.easygoing.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.loserLines.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="D51" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing.polite[1]</t>
+          <t xml:space="preserve">loserLines.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E51" t="inlineStr" s="2">
@@ -1964,7 +1964,7 @@
     <row r="52" ht="40" customHeight="1">
       <c r="A52" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.easygoing.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_MATCH_REACTION.winnerLines.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="D52" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing.polite[1]</t>
+          <t xml:space="preserve">winnerLines.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E52" t="inlineStr" s="2">
@@ -1996,7 +1996,7 @@
     <row r="53" ht="40" customHeight="1">
       <c r="A53" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.easygoing.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateLoser.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="D53" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateLoser.easygoing.polite[1]</t>
+          <t xml:space="preserve">fateLoser.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E53" t="inlineStr" s="2">
@@ -2028,7 +2028,7 @@
     <row r="54" ht="40" customHeight="1">
       <c r="A54" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.easygoing.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.fateWinner.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="D54" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fateWinner.easygoing.polite[1]</t>
+          <t xml:space="preserve">fateWinner.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E54" t="inlineStr" s="2">
@@ -2060,7 +2060,7 @@
     <row r="55" ht="40" customHeight="1">
       <c r="A55" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.easygoing.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.loser.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="D55" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loser.easygoing.polite[1]</t>
+          <t xml:space="preserve">loser.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr" s="2">
@@ -2092,7 +2092,7 @@
     <row r="56" ht="40" customHeight="1">
       <c r="A56" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.easygoing.polite[1]</t>
+          <t xml:space="preserve">RIVALRY_RESOLUTION_LINES.winner.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D56" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winner.easygoing.polite[1]</t>
+          <t xml:space="preserve">winner.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E56" t="inlineStr" s="2">
@@ -2124,7 +2124,7 @@
     <row r="57" ht="40" customHeight="1">
       <c r="A57" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.easygoing.polite[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.loserLines.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="D57" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">loserLines.easygoing.polite[1]</t>
+          <t xml:space="preserve">loserLines.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E57" t="inlineStr" s="2">
@@ -2156,7 +2156,7 @@
     <row r="58" ht="40" customHeight="1">
       <c r="A58" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.easygoing.polite[1]</t>
+          <t xml:space="preserve">UPSET_RIVALRY_LINES.winnerLines.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="D58" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">winnerLines.easygoing.polite[1]</t>
+          <t xml:space="preserve">winnerLines.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E58" t="inlineStr" s="2">
@@ -2956,7 +2956,7 @@
     <row r="83" ht="40" customHeight="1">
       <c r="A83" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.easygoing.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr" s="2">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D83" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.easygoing.polite[1]</t>
+          <t xml:space="preserve">accepted.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E83" t="inlineStr" s="2">
@@ -2988,7 +2988,7 @@
     <row r="84" ht="40" customHeight="1">
       <c r="A84" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.easygoing.polite[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.accepted.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr" s="2">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="D84" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accepted.easygoing.polite[2]</t>
+          <t xml:space="preserve">accepted.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr" s="2">
@@ -3020,7 +3020,7 @@
     <row r="85" ht="40" customHeight="1">
       <c r="A85" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.easygoing.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr" s="2">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D85" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.easygoing.polite[1]</t>
+          <t xml:space="preserve">defended.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E85" t="inlineStr" s="2">
@@ -3052,7 +3052,7 @@
     <row r="86" ht="40" customHeight="1">
       <c r="A86" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.easygoing.polite[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defended.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr" s="2">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="D86" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defended.easygoing.polite[2]</t>
+          <t xml:space="preserve">defended.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr" s="2">
@@ -3084,7 +3084,7 @@
     <row r="87" ht="40" customHeight="1">
       <c r="A87" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.easygoing.polite[1]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr" s="2">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="D87" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.easygoing.polite[1]</t>
+          <t xml:space="preserve">defense_failed.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr" s="2">
@@ -3116,7 +3116,7 @@
     <row r="88" ht="40" customHeight="1">
       <c r="A88" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.easygoing.polite[2]</t>
+          <t xml:space="preserve">POACH_REACTION_DIALOGUES.defense_failed.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr" s="2">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="D88" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defense_failed.easygoing.polite[2]</t>
+          <t xml:space="preserve">defense_failed.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr" s="2">
@@ -3148,7 +3148,7 @@
     <row r="89" ht="40" customHeight="1">
       <c r="A89" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETAIN_LINES.former_champ.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETAIN_LINES.former_champ.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr" s="2">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="D89" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">former_champ.easygoing.polite[1]</t>
+          <t xml:space="preserve">former_champ.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="2">
@@ -3180,7 +3180,7 @@
     <row r="90" ht="40" customHeight="1">
       <c r="A90" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIRE_ACCEPT_LINES.accept_terminal.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr" s="2">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="D90" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">accept_terminal.easygoing.polite[1]</t>
+          <t xml:space="preserve">accept_terminal.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr" s="2">
@@ -3212,7 +3212,7 @@
     <row r="91" ht="40" customHeight="1">
       <c r="A91" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIRE_REFUSE_LINES.refuse_champ.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr" s="2">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="D91" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refuse_champ.easygoing.polite[1]</t>
+          <t xml:space="preserve">refuse_champ.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr" s="2">
@@ -3244,7 +3244,7 @@
     <row r="92" ht="40" customHeight="1">
       <c r="A92" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A1_champion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr" s="2">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="D92" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A1_champion.easygoing.polite[1]</t>
+          <t xml:space="preserve">A1_champion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E92" t="inlineStr" s="2">
@@ -3276,7 +3276,7 @@
     <row r="93" ht="40" customHeight="1">
       <c r="A93" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A2_uncrowned.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr" s="2">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="D93" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A2_uncrowned.easygoing.polite[1]</t>
+          <t xml:space="preserve">A2_uncrowned.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E93" t="inlineStr" s="2">
@@ -3308,7 +3308,7 @@
     <row r="94" ht="40" customHeight="1">
       <c r="A94" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A3_heel.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B94" t="inlineStr" s="2">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="D94" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A3_heel.easygoing.polite[1]</t>
+          <t xml:space="preserve">A3_heel.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E94" t="inlineStr" s="2">
@@ -3340,7 +3340,7 @@
     <row r="95" ht="40" customHeight="1">
       <c r="A95" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.A4_veteran.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B95" t="inlineStr" s="2">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="D95" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">A4_veteran.easygoing.polite[1]</t>
+          <t xml:space="preserve">A4_veteran.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E95" t="inlineStr" s="2">
@@ -3372,7 +3372,7 @@
     <row r="96" ht="40" customHeight="1">
       <c r="A96" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B1_young.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B1_young.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B96" t="inlineStr" s="2">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="D96" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1_young.easygoing.polite[1]</t>
+          <t xml:space="preserve">B1_young.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E96" t="inlineStr" s="2">
@@ -3404,7 +3404,7 @@
     <row r="97" ht="40" customHeight="1">
       <c r="A97" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B2_prime.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B97" t="inlineStr" s="2">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="D97" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2_prime.easygoing.polite[1]</t>
+          <t xml:space="preserve">B2_prime.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr" s="2">
@@ -3436,7 +3436,7 @@
     <row r="98" ht="40" customHeight="1">
       <c r="A98" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B3_older.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B3_older.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B98" t="inlineStr" s="2">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="D98" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3_older.easygoing.polite[1]</t>
+          <t xml:space="preserve">B3_older.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr" s="2">
@@ -3468,7 +3468,7 @@
     <row r="99" ht="40" customHeight="1">
       <c r="A99" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.easygoing.polite[1]</t>
+          <t xml:space="preserve">RETIREMENT_LINES.B4_champion_injury.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B99" t="inlineStr" s="2">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="D99" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_champion_injury.easygoing.polite[1]</t>
+          <t xml:space="preserve">B4_champion_injury.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr" s="2">
@@ -3500,7 +3500,7 @@
     <row r="100" ht="40" customHeight="1">
       <c r="A100" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">VOLUNTARY_STAY_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">VOLUNTARY_STAY_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B100" t="inlineStr" s="2">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="D100" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E100" t="inlineStr" s="2">
@@ -3532,7 +3532,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.easygoing.polite[1]</t>
+          <t xml:space="preserve">raise_accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3564,7 +3564,7 @@
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.easygoing.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3596,7 +3596,7 @@
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.easygoing.polite[1]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3628,7 +3628,7 @@
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.easygoing.polite[1]</t>
+          <t xml:space="preserve">raise_open.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3660,7 +3660,7 @@
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.easygoing.polite[1]</t>
+          <t xml:space="preserve">raise_refuse.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3692,7 +3692,7 @@
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.easygoing.polite[1]</t>
+          <t xml:space="preserve">sudden_departure.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">聞いてくださるんですか？ うーん……{record}なんだかマンネリっていうか。新しいことがしたいんです。</t>
+          <t xml:space="preserve">いやー、ついにこの日が来てしまいましたね。では、お元気で。</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.easygoing.polite[1]</t>
+          <t xml:space="preserve">sudden_departure.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3749,14 +3749,14 @@
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あのですね。{tenure}いろいろ考えたのですが……環境を変えてみたいなと思いまして。</t>
+          <t xml:space="preserve">もう潮時かなと思いまして。楽しかったですよ、ええ。失礼します！</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.easygoing.polite[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.easygoing.polite[2]</t>
+          <t xml:space="preserve">transfer_listen.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3781,14 +3781,14 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー社長、言いにくいのですが。{tenure}少し外の空気を吸ってみたいんです。</t>
+          <t xml:space="preserve">聞いてくださるんですか？ うーん……{record}なんだかマンネリっていうか。新しいことがしたいんです。</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.easygoing.polite[1]</t>
+          <t xml:space="preserve">transfer_open.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3813,14 +3813,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、まあそうなりますよねー。{tenure_farewell}{rivalry}お元気でー！</t>
+          <t xml:space="preserve">社長、あのですね。{tenure}いろいろ考えたのですが……環境を変えてみたいなと思いまして。</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.easygoing.polite[1]</t>
+          <t xml:space="preserve">transfer_open.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3845,14 +3845,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい社長……。お金の問題じゃないんです。もう心が決まってしまって。</t>
+          <t xml:space="preserve">いやー社長、言いにくいのですが。{tenure}少し外の空気を吸ってみたいんです。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.easygoing.polite[1]</t>
+          <t xml:space="preserve">transfer_release.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3877,14 +3877,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、本当ですか？ そこまでしてくださるんですか？ ……じゃあ、もう少しいようかな！</t>
+          <t xml:space="preserve">あはは、まあそうなりますよねー。{tenure_farewell}{rivalry}お元気でー！</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.easygoing.polite[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3909,14 +3909,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">条件次第ですね。…聞かせてください！</t>
+          <t xml:space="preserve">ごめんなさい社長……。お金の問題じゃないんです。もう心が決まってしまって。</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3926,29 +3926,29 @@
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">transfer_retain_success.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか最近調子いいんです！ もっと上に行けそうです！</t>
+          <t xml:space="preserve">え、本当ですか？ そこまでしてくださるんですか？ ……じゃあ、もう少しいようかな！</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3958,29 +3958,29 @@
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">start.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近ちょっとモチベーションが…でも頑張ります</t>
+          <t xml:space="preserve">条件次第ですね。…聞かせてください！</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3990,29 +3990,29 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やる気出てきました！ もう大丈夫です！</t>
+          <t xml:space="preserve">社長、私たちの子のこと、よろしければ思い出してあげてくださいね〜。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4022,29 +4022,29 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子戻ってきました！ もう大丈夫です！</t>
+          <t xml:space="preserve">社長、次のメイン、よろしければ私たちでやらせていただけませんか〜。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4054,29 +4054,29 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.easygoing.polite[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近ちょっと調子悪くて…でも大丈夫です！</t>
+          <t xml:space="preserve">社長、お給料のこと、よろしければ少しご検討いただけませんか〜。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4086,29 +4086,29 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.easygoing.polite[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合でした！ 相手にも感謝です！</t>
+          <t xml:space="preserve">社長、私たちの頑張り、よろしければ一度褒めていただけませんか〜。</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4118,29 +4118,29 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間守り抜きました！ 来年も頑張ります！</t>
+          <t xml:space="preserve">わ、ありがとうございます〜! 社長にそう言ってもらえると本当に嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入りですか…！ 信じられません…ありがとうございます！</t>
+          <t xml:space="preserve">えぇ〜、そうですか〜。失礼しました〜。</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4182,29 +4182,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPですか！ ありがとうございます！ 来年も頑張ります！</t>
+          <t xml:space="preserve">ふぅん、別の形ですか〜。ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4214,29 +4214,29 @@
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うそです…！ 新人王ですか…！ ありがとうございます！</t>
+          <t xml:space="preserve">わ、社長ありがとうございます〜。期待に応えますね!</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4246,29 +4246,29 @@
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム、嬉しいですね。気負わずいきましょう</t>
+          <t xml:space="preserve">えぇ〜、そうですか〜。まあ仕方ないですね。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4278,29 +4278,29 @@
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様と一緒に楽しい時間を作れたら</t>
+          <t xml:space="preserve">ふぅん、別の手ですか〜。ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.easygoing.polite[3]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4310,29 +4310,29 @@
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[3]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ゆったり構えて、精一杯やります</t>
+          <t xml:space="preserve">わ、社長ありがとうございます〜! みんな喜びます!</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4342,29 +4342,29 @@
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員、嬉しいですね。本当に感謝です</t>
+          <t xml:space="preserve">えぇ〜、そうですか〜。承知しました。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4374,29 +4374,29 @@
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みなさんが来てくれたおかげですね</t>
+          <t xml:space="preserve">ふぅん、別の形ですか〜。ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.easygoing.polite[3]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4406,29 +4406,29 @@
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[3]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ゆったりと喜びを噛みしめます</t>
+          <t xml:space="preserve">わ、ありがとうございます〜! 社長に褒めてもらえるなんて!</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4438,29 +4438,29 @@
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと多くの方に見ていただきたくて…出させていただけませんか</t>
+          <t xml:space="preserve">えぇ〜、そうですか〜。失礼しました〜。</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.easygoing.polite[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4470,29 +4470,29 @@
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.easygoing.polite[2]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ、ですか…！ぜひ、出させてください！</t>
+          <t xml:space="preserve">ふぅん、別の形ですか〜。ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4502,29 +4502,29 @@
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったー!信じられない、夢みたい……!</t>
+          <t xml:space="preserve">え、気にされてました〜? ごめんなさい、次は誘いますね〜。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4534,29 +4534,29 @@
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ、一緒に楽しくやりましょう</t>
+          <t xml:space="preserve">ありがとうございます〜! 楽しんできます〜。</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4566,29 +4566,29 @@
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈なプロレスはしないって約束します</t>
+          <t xml:space="preserve">あ、配慮足りなかったですか〜。気をつけます〜。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4598,29 +4598,29 @@
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いしますね〜 楽しみです</t>
+          <t xml:space="preserve">ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4630,29 +4630,29 @@
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっほー、新天地です！暴れまくりますよ</t>
+          <t xml:space="preserve">えぇ〜、お客さんノッてたじゃないですか〜。…はい、控えます〜。</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4662,29 +4662,29 @@
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここなら好き放題やれそうです。楽しみ</t>
+          <t xml:space="preserve">わ、社長わかってる〜! 引き続きやらせていただきます〜。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4694,29 +4694,29 @@
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わーい、今日から仲間です！よろしくお願いします</t>
+          <t xml:space="preserve">あ、ばれてました〜? すみません、明日から出ます〜。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4726,29 +4726,29 @@
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで楽しくやりましょう</t>
+          <t xml:space="preserve">わ、助かります〜、社長ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4758,29 +4758,29 @@
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、ちょっと休みますね〜 すぐ戻ります</t>
+          <t xml:space="preserve">ふぅん、メンバー優先ですか〜。それも助かります〜。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4790,29 +4790,29 @@
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ、一緒に楽しくやりましょう</t>
+          <t xml:space="preserve">わ、見ててくれたんですか〜。じゃ、休ませていただきます〜。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.easygoing.polite[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4822,29 +4822,29 @@
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.easygoing.polite[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈なプロレスはしないって約束します</t>
+          <t xml:space="preserve">いや〜、まだいけます〜。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4854,29 +4854,29 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いしますね〜 楽しみです</t>
+          <t xml:space="preserve">お、メンバーケアですか〜。助かります〜。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4886,29 +4886,29 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリー生活、今日で終わりです！助かりました</t>
+          <t xml:space="preserve">えぇ〜、そんな話あったんですか〜。注意しときます〜。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4918,29 +4918,29 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっほー、新天地です！暴れまくりますよ</t>
+          <t xml:space="preserve">ありがとうございます〜。穏便にいきますね。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.easygoing.polite[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4950,29 +4950,29 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.easygoing.polite[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここなら好き放題やれそうです。楽しみ</t>
+          <t xml:space="preserve">ふぅん、別ルートですか〜。下の子のケア、助かります〜。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4982,29 +4982,29 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わーい、今日から仲間です！よろしくお願いします</t>
+          <t xml:space="preserve">あ、はい〜。気をつけさせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.easygoing.polite[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5014,29 +5014,29 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.easygoing.polite[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで楽しくやりましょう</t>
+          <t xml:space="preserve">（曖昧に笑って、お辞儀した）</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5046,29 +5046,29 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、ちょっと休みますね〜 すぐ戻ります</t>
+          <t xml:space="preserve">ふぅん、別ルートですか〜。ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5078,29 +5078,29 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、ご縁がなかったですね〜 ありがとうございました</t>
+          <t xml:space="preserve">えぇ〜、これくらい大丈夫だと思ったんですけど〜。緩めますね〜。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.polite[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5110,29 +5110,29 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.easygoing.polite[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おじゃましまーす！短い間ですけど暴れますよ</t>
+          <t xml:space="preserve">わ、続けていいんですか〜! ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.easygoing.polite[2]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5142,29 +5142,29 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.easygoing.polite[2]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一時的だからこそ、思い切り好き放題やりますね</t>
+          <t xml:space="preserve">あれ、私じゃなくて子たち優先ですか〜? ありがたいです〜。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.easygoing.polite[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.attack.polite</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5174,29 +5174,29 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.easygoing.polite[1]</t>
+          <t xml:space="preserve">easygoing.attack.polite</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見つけてくださって助かりました！暴れますね</t>
+          <t xml:space="preserve">仲良しごっこは、もう終わりですね</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.polite[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.defend.polite</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5206,29 +5206,29 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.easygoing.polite[1]</t>
+          <t xml:space="preserve">easygoing.defend.polite</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けちゃいましたけど…次はもっといい試合をします</t>
+          <t xml:space="preserve">まあ、仕方ありませんね</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.easygoing.polite[2]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5238,29 +5238,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですけど、下を向いてたら応援してくれる人に失礼ですもんね</t>
+          <t xml:space="preserve">なんか最近調子いいんです！ もっと上に行けそうです！</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.polite[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンはわたしです。また守り切りました</t>
+          <t xml:space="preserve">最近ちょっとモチベーションが…でも頑張ります</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.easygoing.polite[2]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5302,29 +5302,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合でした。また挑戦してきてくださいね</t>
+          <t xml:space="preserve">やる気出てきました！ もう大丈夫です！</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.polite[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5334,29 +5334,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃいました…でもファンが応援してくれる限り、立ち上がります</t>
+          <t xml:space="preserve">調子戻ってきました！ もう大丈夫です！</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.easygoing.polite[2]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5366,29 +5366,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.easygoing.polite[2]</t>
+          <t xml:space="preserve">defeat.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトのない自分なんて想像できませんでした。でも、わたしはわたしですから</t>
+          <t xml:space="preserve">最近ちょっと調子悪くて…でも大丈夫です！</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5398,29 +5398,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.easygoing.polite[1]</t>
+          <t xml:space="preserve">bestMatch.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新チャンピオン誕生です。これからもっと盛り上げます</t>
+          <t xml:space="preserve">最高の試合でした！ 相手にも感謝です！</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.easygoing.polite[2]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5430,29 +5430,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.easygoing.polite[2]</t>
+          <t xml:space="preserve">champion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト獲っちゃいました。最高です</t>
+          <t xml:space="preserve">一年間守り抜きました！ 来年も頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5462,29 +5462,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">hallOfFame.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、ご縁がなかったですね〜 ありがとうございました</t>
+          <t xml:space="preserve">殿堂入りですか…！ 信じられません…ありがとうございます！</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5494,29 +5494,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">mvp.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おじゃましまーす！短い間ですけど暴れますよ</t>
+          <t xml:space="preserve">MVPですか！ ありがとうございます！ 来年も頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5526,29 +5526,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">rookie.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一時的だからこそ、思い切り好き放題やりますね</t>
+          <t xml:space="preserve">うそです…！ 新人王ですか…！ ありがとうございます！</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5558,29 +5558,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けちゃいましたけど…次はもっといい試合をします</t>
+          <t xml:space="preserve">ドーム、嬉しいですね。気負わずいきましょう</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5590,29 +5590,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですけど、下を向いてたら応援してくれる人に失礼ですもんね</t>
+          <t xml:space="preserve">お客様と一緒に楽しい時間を作れたら</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.easygoing[3]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5622,29 +5622,29 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[3]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンはわたしです。また守り切りました</t>
+          <t xml:space="preserve">ゆったり構えて、精一杯やります</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5654,29 +5654,29 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合でした。また挑戦してきてくださいね</t>
+          <t xml:space="preserve">満員、嬉しいですね。本当に感謝です</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5686,29 +5686,29 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃいました…でもファンが応援してくれる限り、立ち上がります</t>
+          <t xml:space="preserve">みなさんが来てくれたおかげですね</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.easygoing[3]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5718,29 +5718,29 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[3]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトのない自分なんて想像できませんでした。でも、わたしはわたしですから</t>
+          <t xml:space="preserve">ゆったりと喜びを噛みしめます</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5750,29 +5750,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">E1.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新チャンピオン誕生です。これからもっと盛り上げます</t>
+          <t xml:space="preserve">もっと多くの方に見ていただきたくて…出させていただけませんか</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.easygoing.polite[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5782,29 +5782,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[2]</t>
+          <t xml:space="preserve">E1.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト獲っちゃいました。最高です</t>
+          <t xml:space="preserve">テレビ、ですか…！ぜひ、出させてください！</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5814,29 +5814,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">E1.accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、ちょっと合わないかもしれません…</t>
+          <t xml:space="preserve">やったー!信じられない、夢みたい……!</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5846,29 +5846,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ〜、最近ちょっと素っ気ないような…</t>
+          <t xml:space="preserve">えへへ、一緒に楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5878,29 +5878,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ん〜、なんだか少し空気が変わりましたかね〜</t>
+          <t xml:space="preserve">退屈なプロレスはしないって約束します</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5910,29 +5910,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気楽にお付き合いできて嬉しいです〜</t>
+          <t xml:space="preserve">よろしくお願いしますね〜 楽しみです</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5942,29 +5942,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の相棒です〜。ずっと一緒にいたいですね</t>
+          <t xml:space="preserve">やっほー、新天地です！暴れまくりますよ</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5974,29 +5974,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒だと、何もかも上手くいく気がするんです</t>
+          <t xml:space="preserve">ここなら好き放題やれそうです。楽しみ</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6006,29 +6006,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い関係も一段落ですね。ちょっと寂しいです</t>
+          <t xml:space="preserve">わーい、今日から仲間です！よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6038,29 +6038,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ因縁も永遠じゃありませんよね〜</t>
+          <t xml:space="preserve">みんなで楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6070,29 +6070,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい勝負になりそうですね〜。燃えてきました</t>
+          <t xml:space="preserve">あ、ちょっと休みますね〜 すぐ戻ります</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6102,29 +6102,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">draftInterest.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、負けたくないです〜</t>
+          <t xml:space="preserve">えへへ、一緒に楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6134,29 +6134,29 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">draftInterest.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本気でやり合いたい相手なんて、そういませんよ〜</t>
+          <t xml:space="preserve">退屈なプロレスはしないって約束します</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6166,29 +6166,29 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">draftJoin.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、考えると自然と気合が入ります</t>
+          <t xml:space="preserve">よろしくお願いしますね〜 楽しみです</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6198,29 +6198,29 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">faGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この試合が一番楽しいんです。ずっとこの関係が続けばいいのに</t>
+          <t xml:space="preserve">フリー生活、今日で終わりです！助かりました</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6230,29 +6230,29 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">faSigning.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命のライバルですね〜。最高です</t>
+          <t xml:space="preserve">やっほー、新天地です！暴れまくりますよ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6262,29 +6262,29 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.polite[1]</t>
+          <t xml:space="preserve">faSigning.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここ最高です〜！ みんなとやるの楽しいです！</t>
+          <t xml:space="preserve">ここなら好き放題やれそうです。楽しみ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6294,29 +6294,29 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.polite[2]</t>
+          <t xml:space="preserve">faWelcome.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、すっごく居心地いいんですよね〜</t>
+          <t xml:space="preserve">わーい、今日から仲間です！よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6326,29 +6326,29 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.polite[1]</t>
+          <t xml:space="preserve">faWelcome.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがにこれは…笑えないですね</t>
+          <t xml:space="preserve">みんなで楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6358,29 +6358,29 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.polite[2]</t>
+          <t xml:space="preserve">injury.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは…なんて笑っている場合じゃないですよね、これ</t>
+          <t xml:space="preserve">あ、ちょっと休みますね〜 すぐ戻ります</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6390,29 +6390,29 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.polite[1]</t>
+          <t xml:space="preserve">release.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、最近ちょっとモヤモヤします…</t>
+          <t xml:space="preserve">あはは、ご縁がなかったですね〜 ありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6422,29 +6422,29 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.polite[2]</t>
+          <t xml:space="preserve">rentalGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ大丈夫…ですよね？ ちょっと不安ですけど</t>
+          <t xml:space="preserve">おじゃましまーす！短い間ですけど暴れますよ</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6454,29 +6454,29 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝ストップかあ…でもまた頑張ります！</t>
+          <t xml:space="preserve">一時的だからこそ、思い切り好き放題やりますね</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6486,29 +6486,29 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.polite[1]</t>
+          <t xml:space="preserve">scoutGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、身体はもうへとへとです。でも、最後まで頑張りますよ</t>
+          <t xml:space="preserve">見つけてくださって助かりました！暴れますね</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6518,29 +6518,29 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.easygoing.polite[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たら、やるしかないですよね。痛いけど、まあいっか</t>
+          <t xml:space="preserve">今日は負けちゃいましたけど…次はもっといい試合をします</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6550,29 +6550,29 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.polite[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手の方ですね。えーと、気楽に…いや、ちゃんとやります</t>
+          <t xml:space="preserve">悔しいですけど、下を向いてたら応援してくれる人に失礼ですもんね</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6582,29 +6582,29 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.easygoing.polite[2]</t>
+          <t xml:space="preserve">titleDefense.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつ、しっかりお相手しますよ。ま、任せてください</t>
+          <t xml:space="preserve">チャンピオンはわたしです。また守り切りました</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6614,29 +6614,29 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.polite[1]</t>
+          <t xml:space="preserve">titleDefense.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、倒せました。…はぁ、疲れましたけど、まだ退けません。次の方、どうぞ</t>
+          <t xml:space="preserve">いい試合でした。また挑戦してきてくださいね</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6646,29 +6646,29 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.easygoing.polite[2]</t>
+          <t xml:space="preserve">titleLoss.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふう、一人おしまいです。でも、まだ立ってますよ。次、来てくださいねー</t>
+          <t xml:space="preserve">負けちゃいました…でもファンが応援してくれる限り、立ち上がります</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6678,29 +6678,29 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.polite[1]</t>
+          <t xml:space="preserve">titleLoss.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高のチームでしたよね。三人で勝てて、本当に嬉しいです</t>
+          <t xml:space="preserve">…ベルトのない自分なんて想像できませんでした。でも、わたしはわたしですから</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6710,29 +6710,29 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.easygoing.polite[2]</t>
+          <t xml:space="preserve">titleWin.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間がいてくれたから、のびのびやれました。ありがとうございます</t>
+          <t xml:space="preserve">新チャンピオン誕生です。これからもっと盛り上げます</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6742,29 +6742,29 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.polite[1]</t>
+          <t xml:space="preserve">titleWin.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPはありがたいですけど……やっぱり、みんなで勝ちたかったですね</t>
+          <t xml:space="preserve">ベルト獲っちゃいました。最高です</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6774,29 +6774,29 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は三人揃って笑えるように。そう思ってます</t>
+          <t xml:space="preserve">あはは、ご縁がなかったですね〜 ありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6806,29 +6806,29 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、何人来たか覚えてないです。でも、全部楽しかったですよ</t>
+          <t xml:space="preserve">おじゃましまーす！短い間ですけど暴れますよ</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6838,29 +6838,29 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足がふらふらしてますけど……全員倒したから、まあいっかって感じです</t>
+          <t xml:space="preserve">一時的だからこそ、思い切り好き放題やりますね</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6870,29 +6870,29 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で行きます！ よろしくお願いします！</t>
+          <t xml:space="preserve">今日は負けちゃいましたけど…次はもっといい試合をします</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6902,29 +6902,29 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった、勝ちました!最高の舞台で最高の結果、夢みたいです!</t>
+          <t xml:space="preserve">悔しいですけど、下を向いてたら応援してくれる人に失礼ですもんね</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6934,29 +6934,29 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました！ うちの団体の底力を見せられましたね！</t>
+          <t xml:space="preserve">チャンピオンはわたしです。また守り切りました</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6966,29 +6966,29 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後まで楽しかったです！ ありがとうございました！</t>
+          <t xml:space="preserve">いい試合でした。また挑戦してきてくださいね</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6998,29 +6998,29 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリー生活、今日で終わりです！助かりました</t>
+          <t xml:space="preserve">負けちゃいました…でもファンが応援してくれる限り、立ち上がります</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SCOUT_GREETING_LINES.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7030,27 +7030,1339 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">…ベルトのない自分なんて想像できませんでした。でも、わたしはわたしですから</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="40" customHeight="1">
+      <c r="A211" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">新チャンピオン誕生です。これからもっと盛り上げます</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="40" customHeight="1">
+      <c r="A212" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">12 選手経歴イベント</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ベルト獲っちゃいました。最高です</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="40" customHeight="1">
+      <c r="A213" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_39_down.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">う〜ん、ちょっと合わないかもしれません…</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="40" customHeight="1">
+      <c r="A214" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あれ〜、最近ちょっと素っ気ないような…</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="40" customHeight="1">
+      <c r="A215" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_59_down.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ん〜、なんだか少し空気が変わりましたかね〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="40" customHeight="1">
+      <c r="A216" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_60_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">気楽にお付き合いできて嬉しいです〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="40" customHeight="1">
+      <c r="A217" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高の相棒です〜。ずっと一緒にいたいですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="40" customHeight="1">
+      <c r="A218" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">bond_80_up.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一緒だと、何もかも上手くいく気がするんです</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="40" customHeight="1">
+      <c r="A219" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">熱い関係も一段落ですね。ちょっと寂しいです</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="40" customHeight="1">
+      <c r="A220" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_29_down.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まぁ因縁も永遠じゃありませんよね〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="40" customHeight="1">
+      <c r="A221" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">いい勝負になりそうですね〜。燃えてきました</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="40" customHeight="1">
+      <c r="A222" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_30_up.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あはは、負けたくないです〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="40" customHeight="1">
+      <c r="A223" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">本気でやり合いたい相手なんて、そういませんよ〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="40" customHeight="1">
+      <c r="A224" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_50_up.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふふ、考えると自然と気合が入ります</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="40" customHeight="1">
+      <c r="A225" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この試合が一番楽しいんです。ずっとこの関係が続けばいいのに</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="40" customHeight="1">
+      <c r="A226" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">rivalry_70_up.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">運命のライバルですね〜。最高です</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="40" customHeight="1">
+      <c r="A227" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここ最高です〜！ みんなとやるの楽しいです！</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="40" customHeight="1">
+      <c r="A228" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_above_75.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">この団体、すっごく居心地いいんですよね〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="40" customHeight="1">
+      <c r="A229" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">さすがにこれは…笑えないですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="40" customHeight="1">
+      <c r="A230" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_20.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あはは…なんて笑っている場合じゃないですよね、これ</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="40" customHeight="1">
+      <c r="A231" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.easygoing.polite[1]</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">う〜ん、最近ちょっとモヤモヤします…</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="40" customHeight="1">
+      <c r="A232" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">trust_below_35.easygoing.polite[2]</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">まぁ大丈夫…ですよね？ ちょっと不安ですけど</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="40" customHeight="1">
+      <c r="A233" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">連勝ストップかあ…でもまた頑張ります！</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="40" customHeight="1">
+      <c r="A234" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あはは、身体はもうへとへとです。でも、最後まで頑張りますよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="40" customHeight="1">
+      <c r="A235" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preFinal.polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ここまで来たら、やるしかないですよね。痛いけど、まあいっか</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="40" customHeight="1">
+      <c r="A236" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">相手の方ですね。えーと、気楽に…いや、ちゃんとやります</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="40" customHeight="1">
+      <c r="A237" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">preMatch.polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一戦ずつ、しっかりお相手しますよ。ま、任せてください</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="40" customHeight="1">
+      <c r="A238" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">一人、倒せました。…はぁ、疲れましたけど、まだ退けません。次の方、どうぞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="40" customHeight="1">
+      <c r="A239" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">survivor.polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">ふう、一人おしまいです。でも、まだ立ってますよ。次、来てくださいねー</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="40" customHeight="1">
+      <c r="A240" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最高のチームでしたよね。三人で勝てて、本当に嬉しいです</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="40" customHeight="1">
+      <c r="A241" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">champion.polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">仲間がいてくれたから、のびのびやれました。ありがとうございます</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="40" customHeight="1">
+      <c r="A242" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">MVPはありがたいですけど……やっぱり、みんなで勝ちたかったですね</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="40" customHeight="1">
+      <c r="A243" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">defiant.polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">次は三人揃って笑えるように。そう思ってます</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="40" customHeight="1">
+      <c r="A244" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あはは、何人来たか覚えてないです。でも、全部楽しかったですよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="40" customHeight="1">
+      <c r="A245" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">足がふらふらしてますけど……全員倒したから、まあいっかって感じです</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="40" customHeight="1">
+      <c r="A246" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力で行きます！ よろしくお願いします！</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="40" customHeight="1">
+      <c r="A247" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やった、勝ちました!最高の舞台で最高の結果、夢みたいです!</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="40" customHeight="1">
+      <c r="A248" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちました！ うちの団体の底力を見せられましたね！</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="40" customHeight="1">
+      <c r="A249" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後まで楽しかったです！ ありがとうございました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="40" customHeight="1">
+      <c r="A250" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">フリー生活、今日で終わりです！助かりました</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="40" customHeight="1">
+      <c r="A251" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">SCOUT_GREETING_LINES.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">easygoing.polite[1]</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr" s="2">
+      <c r="D251" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr" s="3">
+      <c r="F251" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">見つけてくださって助かりました！暴れますね</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H210"/>
+  <autoFilter ref="A1:H251"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×お気楽.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H251"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="F14" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい、もっとやれたはずなのに…次こそ、絶対頑張ります!</t>
+          <t xml:space="preserve">ごめんなさい、もっとやれたはずなのに…次こそ、絶対頑張ります！</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="F15" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなの声、届いてました!最高の試合でした、ありがとうございます!</t>
+          <t xml:space="preserve">みんなの声、届いてました！最高の試合でした、ありがとうございます！</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="F16" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、争奪戦ですか!?嬉しいです、頑張ります!</t>
+          <t xml:space="preserve">え、争奪戦ですか！？嬉しいです、頑張ります！</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="F17" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いします!楽しくやっていきましょう!</t>
+          <t xml:space="preserve">よろしくお願いします！楽しくやっていきましょう！</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="F18" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリーも気楽でしたけど、団体に入るのも楽しそうです!よろしくお願いします!</t>
+          <t xml:space="preserve">フリーも気楽でしたけど、団体に入るのも楽しそうです！よろしくお願いします！</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="F21" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">要らないって言われた身なんですけど、勝っちゃいました。いいんですか?</t>
+          <t xml:space="preserve">要らないって言われた身なんですけど、勝っちゃいました。いいんですか？</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="F22" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あそこ、私を切ったの…ちょっと早まりましたね?</t>
+          <t xml:space="preserve">あそこ、私を切ったの…ちょっと早まりましたね？</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F34" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここからはわたしの出番です♪</t>
+          <t xml:space="preserve">ここからは私の出番です♪</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="F71" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あら、わたしですか。いいですよ、やりましょう。</t>
+          <t xml:space="preserve">あら、私ですか。いいですよ、やりましょう。</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="F100" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">残らせていただきますね!ここ、すごく楽しいんです!</t>
+          <t xml:space="preserve">残らせていただきますね！ここ、すごく楽しいんです！</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、ありがとうございます〜! 社長にそう言ってもらえると本当に嬉しいです。</t>
+          <t xml:space="preserve">わ、ありがとうございます〜！ 社長にそう言ってもらえると本当に嬉しいです。</t>
         </is>
       </c>
     </row>
@@ -4229,7 +4229,7 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、社長ありがとうございます〜。期待に応えますね!</t>
+          <t xml:space="preserve">わ、社長ありがとうございます〜。期待に応えますね！</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4325,7 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、社長ありがとうございます〜! みんな喜びます!</t>
+          <t xml:space="preserve">わ、社長ありがとうございます〜！ みんな喜びます！</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、ありがとうございます〜! 社長に褒めてもらえるなんて!</t>
+          <t xml:space="preserve">わ、ありがとうございます〜！ 社長に褒めてもらえるなんて！</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、気にされてました〜? ごめんなさい、次は誘いますね〜。</t>
+          <t xml:space="preserve">え、気にされてました〜？ ごめんなさい、次は誘いますね〜。</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます〜! 楽しんできます〜。</t>
+          <t xml:space="preserve">ありがとうございます〜！ 楽しんできます〜。</t>
         </is>
       </c>
     </row>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、社長わかってる〜! 引き続きやらせていただきます〜。</t>
+          <t xml:space="preserve">わ、社長わかってる〜！ 引き続きやらせていただきます〜。</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、ばれてました〜? すみません、明日から出ます〜。</t>
+          <t xml:space="preserve">あ、ばれてました〜？ すみません、明日から出ます〜。</t>
         </is>
       </c>
     </row>
@@ -5125,7 +5125,7 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、続けていいんですか〜! ありがとうございます〜。</t>
+          <t xml:space="preserve">わ、続けていいんですか〜！ ありがとうございます〜。</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ、私じゃなくて子たち優先ですか〜? ありがたいです〜。</t>
+          <t xml:space="preserve">あれ、私じゃなくて子たち優先ですか〜？ ありがたいです〜。</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲良しごっこは、もう終わりですね</t>
+          <t xml:space="preserve">仲良しはここまでですね！　さあ、本気でいきましょう！</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.polite.easygoing[1]</t>
+          <t xml:space="preserve">autumnWarChampion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
@@ -5413,14 +5413,14 @@
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合でした！ 相手にも感謝です！</t>
+          <t xml:space="preserve">みんなと一緒に喜べる優勝って、最高ですね。</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.polite.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.easygoing[1]</t>
+          <t xml:space="preserve">bestMatch.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
@@ -5445,14 +5445,14 @@
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間守り抜きました！ 来年も頑張ります！</t>
+          <t xml:space="preserve">最高の試合でした！ 相手にも感謝です！</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.polite.easygoing[1]</t>
+          <t xml:space="preserve">champion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
@@ -5477,14 +5477,14 @@
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入りですか…！ 信じられません…ありがとうございます！</t>
+          <t xml:space="preserve">一年間守り抜きました！ 来年も頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.polite.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.polite.easygoing[1]</t>
+          <t xml:space="preserve">hallOfFame.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
@@ -5509,14 +5509,14 @@
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPですか！ ありがとうございます！ 来年も頑張ります！</t>
+          <t xml:space="preserve">殿堂入りですか…！ 信じられません…ありがとうございます！</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.polite.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.polite.easygoing[1]</t>
+          <t xml:space="preserve">mvp.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
@@ -5541,14 +5541,14 @@
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うそです…！ 新人王ですか…！ ありがとうございます！</t>
+          <t xml:space="preserve">MVPですか！ ありがとうございます！ 来年も頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">rookie.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
@@ -5573,14 +5573,14 @@
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム、嬉しいですね。気負わずいきましょう</t>
+          <t xml:space="preserve">うそです…！ 新人王ですか…！ ありがとうございます！</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[2]</t>
+          <t xml:space="preserve">springTagChampion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
@@ -5605,14 +5605,14 @@
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様と一緒に楽しい時間を作れたら</t>
+          <t xml:space="preserve">相棒と優勝できて、本当にうれしいです。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.easygoing[3]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[3]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5637,14 +5637,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ゆったり構えて、精一杯やります</t>
+          <t xml:space="preserve">ドーム、嬉しいですね。気負わずいきましょう</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5669,14 +5669,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員、嬉しいですね。本当に感謝です</t>
+          <t xml:space="preserve">お客様と一緒に楽しい時間を作れたら</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.easygoing[3]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[2]</t>
+          <t xml:space="preserve">polite.easygoing[3]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5701,14 +5701,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みなさんが来てくれたおかげですね</t>
+          <t xml:space="preserve">ゆったり構えて、精一杯やります</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.easygoing[3]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[3]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5733,14 +5733,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ゆったりと喜びを噛みしめます</t>
+          <t xml:space="preserve">満員、嬉しいですね。本当に感謝です</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5750,29 +5750,29 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと多くの方に見ていただきたくて…出させていただけませんか</t>
+          <t xml:space="preserve">みなさんが来てくれたおかげですね</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.easygoing[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.easygoing[3]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5782,29 +5782,29 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.polite.easygoing[2]</t>
+          <t xml:space="preserve">polite.easygoing[3]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ、ですか…！ぜひ、出させてください！</t>
+          <t xml:space="preserve">ゆったりと喜びを噛みしめます</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.polite.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.polite.easygoing[1]</t>
+          <t xml:space="preserve">E1.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
@@ -5829,14 +5829,14 @@
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったー!信じられない、夢みたい……!</t>
+          <t xml:space="preserve">もっと多くの方に見ていただきたくて…出させていただけませんか</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5846,29 +5846,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">E1.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ、一緒に楽しくやりましょう</t>
+          <t xml:space="preserve">テレビ、ですか…！ぜひ、出させてください！</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5878,29 +5878,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[2]</t>
+          <t xml:space="preserve">E1.accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈なプロレスはしないって約束します</t>
+          <t xml:space="preserve">やったー！信じられない、夢みたい……！</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
@@ -5925,14 +5925,14 @@
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いしますね〜 楽しみです</t>
+          <t xml:space="preserve">えへへ、一緒に楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
@@ -5957,14 +5957,14 @@
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっほー、新天地です！暴れまくりますよ</t>
+          <t xml:space="preserve">退屈なプロレスはしないって約束します</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5974,12 +5974,12 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[2]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
@@ -5989,14 +5989,14 @@
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここなら好き放題やれそうです。楽しみ</t>
+          <t xml:space="preserve">よろしくお願いしますね〜 楽しみです</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6006,7 +6006,7 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
@@ -6021,14 +6021,14 @@
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わーい、今日から仲間です！よろしくお願いします</t>
+          <t xml:space="preserve">やっほー、新天地です！暴れまくりますよ</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
@@ -6053,14 +6053,14 @@
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで楽しくやりましょう</t>
+          <t xml:space="preserve">ここなら好き放題やれそうです。楽しみ</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
@@ -6085,14 +6085,14 @@
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、ちょっと休みますね〜 すぐ戻ります</t>
+          <t xml:space="preserve">わーい、今日から仲間です！よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
@@ -6117,14 +6117,14 @@
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ、一緒に楽しくやりましょう</t>
+          <t xml:space="preserve">みんなで楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.polite.easygoing[2]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr" s="2">
@@ -6149,14 +6149,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈なプロレスはしないって約束します</t>
+          <t xml:space="preserve">あ、ちょっと休みますね〜 すぐ戻ります</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.polite.easygoing[1]</t>
+          <t xml:space="preserve">draftInterest.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6181,14 +6181,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いしますね〜 楽しみです</t>
+          <t xml:space="preserve">えへへ、一緒に楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.polite.easygoing[1]</t>
+          <t xml:space="preserve">draftInterest.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6213,14 +6213,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリー生活、今日で終わりです！助かりました</t>
+          <t xml:space="preserve">退屈なプロレスはしないって約束します</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.polite.easygoing[1]</t>
+          <t xml:space="preserve">draftJoin.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6245,14 +6245,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっほー、新天地です！暴れまくりますよ</t>
+          <t xml:space="preserve">よろしくお願いしますね〜 楽しみです</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.polite.easygoing[2]</t>
+          <t xml:space="preserve">faGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6277,14 +6277,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここなら好き放題やれそうです。楽しみ</t>
+          <t xml:space="preserve">フリー生活は今日で卒業です！　ここから楽しくなりそう！</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.polite.easygoing[1]</t>
+          <t xml:space="preserve">faSigning.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6309,14 +6309,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わーい、今日から仲間です！よろしくお願いします</t>
+          <t xml:space="preserve">やっほー、新天地です！暴れまくりますよ</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.polite.easygoing[2]</t>
+          <t xml:space="preserve">faSigning.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6341,14 +6341,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで楽しくやりましょう</t>
+          <t xml:space="preserve">ここなら好き放題やれそうです。楽しみ</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.polite.easygoing[1]</t>
+          <t xml:space="preserve">faWelcome.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6373,14 +6373,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、ちょっと休みますね〜 すぐ戻ります</t>
+          <t xml:space="preserve">わーい、今日から仲間です！よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.polite.easygoing[1]</t>
+          <t xml:space="preserve">faWelcome.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6405,14 +6405,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、ご縁がなかったですね〜 ありがとうございました</t>
+          <t xml:space="preserve">みんなで楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.polite.easygoing[1]</t>
+          <t xml:space="preserve">injury.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6437,14 +6437,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おじゃましまーす！短い間ですけど暴れますよ</t>
+          <t xml:space="preserve">あ、ちょっと休みますね〜 すぐ戻ります</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.polite.easygoing[2]</t>
+          <t xml:space="preserve">release.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6469,14 +6469,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一時的だからこそ、思い切り好き放題やりますね</t>
+          <t xml:space="preserve">あはは、ご縁がなかったですね〜 ありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.polite.easygoing[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6501,14 +6501,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">見つけてくださって助かりました！暴れますね</t>
+          <t xml:space="preserve">おじゃましまーす！短い間ですけど暴れますよ</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.polite.easygoing[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6533,14 +6533,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けちゃいましたけど…次はもっといい試合をします</t>
+          <t xml:space="preserve">一時的だからこそ、思い切り好き放題やりますね</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.polite.easygoing[2]</t>
+          <t xml:space="preserve">scoutGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6565,14 +6565,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですけど、下を向いてたら応援してくれる人に失礼ですもんね</t>
+          <t xml:space="preserve">声をかけてくださって嬉しいです！　思いきり暴れますね！</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.polite.easygoing[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6597,14 +6597,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンはわたしです。また守り切りました</t>
+          <t xml:space="preserve">今日は負けちゃいましたけど…次はもっといい試合をします</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.polite.easygoing[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6629,14 +6629,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合でした。また挑戦してきてくださいね</t>
+          <t xml:space="preserve">悔しいですけど、下を向いてたら応援してくれる人に失礼ですもんね</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.polite.easygoing[1]</t>
+          <t xml:space="preserve">titleDefense.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6661,14 +6661,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃいました…でもファンが応援してくれる限り、立ち上がります</t>
+          <t xml:space="preserve">チャンピオンは私です。また守り切りました</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.polite.easygoing[2]</t>
+          <t xml:space="preserve">titleDefense.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6693,14 +6693,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトのない自分なんて想像できませんでした。でも、わたしはわたしですから</t>
+          <t xml:space="preserve">いい試合でした。また挑戦してきてくださいね</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.polite.easygoing[1]</t>
+          <t xml:space="preserve">titleLoss.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6725,14 +6725,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新チャンピオン誕生です。これからもっと盛り上げます</t>
+          <t xml:space="preserve">負けちゃいました…でもファンが応援してくれる限り、立ち上がります</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.polite.easygoing[2]</t>
+          <t xml:space="preserve">titleLoss.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6757,14 +6757,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト獲っちゃいました。最高です</t>
+          <t xml:space="preserve">…ベルトのない自分なんて想像できませんでした。でも、私は私ですから</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">titleWin.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6789,14 +6789,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、ご縁がなかったですね〜 ありがとうございました</t>
+          <t xml:space="preserve">新チャンピオン誕生です。これからもっと盛り上げます</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6806,12 +6806,12 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">titleWin.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6821,14 +6821,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おじゃましまーす！短い間ですけど暴れますよ</t>
+          <t xml:space="preserve">ベルト獲っちゃいました。最高です</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[2]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6853,14 +6853,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一時的だからこそ、思い切り好き放題やりますね</t>
+          <t xml:space="preserve">あはは、ご縁がなかったですね〜 ありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
@@ -6885,14 +6885,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けちゃいましたけど…次はもっといい試合をします</t>
+          <t xml:space="preserve">おじゃましまーす！短い間ですけど暴れますよ</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
@@ -6917,14 +6917,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですけど、下を向いてたら応援してくれる人に失礼ですもんね</t>
+          <t xml:space="preserve">一時的だからこそ、思い切り好き放題やりますね</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
@@ -6949,14 +6949,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンはわたしです。また守り切りました</t>
+          <t xml:space="preserve">今日は負けちゃいましたけど…次はもっといい試合をします</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
@@ -6981,14 +6981,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合でした。また挑戦してきてくださいね</t>
+          <t xml:space="preserve">悔しいですけど、下を向いてたら応援してくれる人に失礼ですもんね</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
@@ -7013,14 +7013,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃいました…でもファンが応援してくれる限り、立ち上がります</t>
+          <t xml:space="preserve">チャンピオンは私です。また守り切りました</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
@@ -7045,14 +7045,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトのない自分なんて想像できませんでした。でも、わたしはわたしですから</t>
+          <t xml:space="preserve">いい試合でした。また挑戦してきてくださいね</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
@@ -7077,14 +7077,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新チャンピオン誕生です。これからもっと盛り上げます</t>
+          <t xml:space="preserve">負けちゃいました…でもファンが応援してくれる限り、立ち上がります</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
@@ -7109,14 +7109,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト獲っちゃいました。最高です</t>
+          <t xml:space="preserve">…ベルトのない自分なんて想像できませんでした。でも、私は私ですから</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7126,29 +7126,29 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、ちょっと合わないかもしれません…</t>
+          <t xml:space="preserve">新チャンピオン誕生です。これからもっと盛り上げます</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7158,29 +7158,29 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ〜、最近ちょっと素っ気ないような…</t>
+          <t xml:space="preserve">ベルト獲っちゃいました。最高です</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.polite[2]</t>
+          <t xml:space="preserve">bond_39_down.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
@@ -7205,14 +7205,14 @@
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ん〜、なんだか少し空気が変わりましたかね〜</t>
+          <t xml:space="preserve">う〜ん、ちょっと合わないかもしれません…</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
@@ -7237,14 +7237,14 @@
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気楽にお付き合いできて嬉しいです〜</t>
+          <t xml:space="preserve">あれ〜、最近ちょっと素っ気ないような…</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
@@ -7269,14 +7269,14 @@
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の相棒です〜。ずっと一緒にいたいですね</t>
+          <t xml:space="preserve">ん〜、なんだか少し空気が変わりましたかね〜</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
@@ -7301,14 +7301,14 @@
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒だと、何もかも上手くいく気がするんです</t>
+          <t xml:space="preserve">気楽にお付き合いできて嬉しいです〜</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
@@ -7333,14 +7333,14 @@
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い関係も一段落ですね。ちょっと寂しいです</t>
+          <t xml:space="preserve">最高の相棒です〜。ずっと一緒にいたいですね</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7355,7 +7355,7 @@
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.polite[2]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
@@ -7365,14 +7365,14 @@
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ因縁も永遠じゃありませんよね〜</t>
+          <t xml:space="preserve">一緒だと、何もかも上手くいく気がするんです</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
@@ -7397,14 +7397,14 @@
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい勝負になりそうですね〜。燃えてきました</t>
+          <t xml:space="preserve">熱い関係も一段落ですね。ちょっと寂しいです</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7429,14 +7429,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、負けたくないです〜</t>
+          <t xml:space="preserve">まぁ因縁も永遠じゃありませんよね〜</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7461,14 +7461,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本気でやり合いたい相手なんて、そういませんよ〜</t>
+          <t xml:space="preserve">いい勝負になりそうですね〜。燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7493,14 +7493,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、考えると自然と気合が入ります</t>
+          <t xml:space="preserve">あはは、負けたくないです〜</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7525,14 +7525,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この試合が一番楽しいんです。ずっとこの関係が続けばいいのに</t>
+          <t xml:space="preserve">本気でやり合いたい相手なんて、そういませんよ〜</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7557,14 +7557,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命のライバルですね〜。最高です</t>
+          <t xml:space="preserve">ふふ、考えると自然と気合が入ります</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.polite[1]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7589,14 +7589,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここ最高です〜！ みんなとやるの楽しいです！</t>
+          <t xml:space="preserve">この試合が一番楽しいんです。ずっとこの関係が続けばいいのに</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.polite[2]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7621,14 +7621,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、すっごく居心地いいんですよね〜</t>
+          <t xml:space="preserve">運命のライバルですね〜。最高です</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.polite[1]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7653,14 +7653,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがにこれは…笑えないですね</t>
+          <t xml:space="preserve">ここ最高です〜！ みんなとやるの楽しいです！</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.polite[2]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7685,14 +7685,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは…なんて笑っている場合じゃないですよね、これ</t>
+          <t xml:space="preserve">この団体、すっごく居心地いいんですよね〜</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.polite[1]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7717,14 +7717,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、最近ちょっとモヤモヤします…</t>
+          <t xml:space="preserve">さすがにこれは…笑えないですね</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.polite[2]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7749,14 +7749,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ大丈夫…ですよね？ ちょっと不安ですけど</t>
+          <t xml:space="preserve">あはは…なんて笑っている場合じゃないですよね、これ</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7781,14 +7781,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝ストップかあ…でもまた頑張ります！</t>
+          <t xml:space="preserve">う〜ん、最近ちょっとモヤモヤします…</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7798,29 +7798,29 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、身体はもうへとへとです。でも、最後まで頑張りますよ</t>
+          <t xml:space="preserve">まぁ大丈夫…ですよね？ ちょっと不安ですけど</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7830,29 +7830,29 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.easygoing[2]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たら、やるしかないですよね。痛いけど、まあいっか</t>
+          <t xml:space="preserve">連勝ストップかあ…でもまた頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
@@ -7877,14 +7877,14 @@
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手の方ですね。えーと、気楽に…いや、ちゃんとやります</t>
+          <t xml:space="preserve">あはは、身体はもうへとへとです。でも、最後まで頑張りますよ</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
@@ -7909,14 +7909,14 @@
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつ、しっかりお相手しますよ。ま、任せてください</t>
+          <t xml:space="preserve">ここまで来たら、やるしかないですよね。痛いけど、まあいっか</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
@@ -7941,14 +7941,14 @@
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、倒せました。…はぁ、疲れましたけど、まだ退けません。次の方、どうぞ</t>
+          <t xml:space="preserve">相手の方ですね。えーと、気楽に…いや、ちゃんとやります</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
@@ -7973,14 +7973,14 @@
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふう、一人おしまいです。でも、まだ立ってますよ。次、来てくださいねー</t>
+          <t xml:space="preserve">一戦ずつ、しっかりお相手しますよ。ま、任せてください</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.easygoing[1]</t>
+          <t xml:space="preserve">survivor.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
@@ -8005,14 +8005,14 @@
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高のチームでしたよね。三人で勝てて、本当に嬉しいです</t>
+          <t xml:space="preserve">一人、倒せました。…はぁ、疲れましたけど、まだ退けません。次の方、どうぞ</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.easygoing[2]</t>
+          <t xml:space="preserve">survivor.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
@@ -8037,14 +8037,14 @@
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間がいてくれたから、のびのびやれました。ありがとうございます</t>
+          <t xml:space="preserve">ふう、一人おしまいです。でも、まだ立ってますよ。次、来てくださいねー</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.easygoing[1]</t>
+          <t xml:space="preserve">champion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
@@ -8069,14 +8069,14 @@
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPはありがたいですけど……やっぱり、みんなで勝ちたかったですね</t>
+          <t xml:space="preserve">最高のチームでしたよね。三人で勝てて、本当に嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.easygoing[2]</t>
+          <t xml:space="preserve">champion.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8101,14 +8101,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は三人揃って笑えるように。そう思ってます</t>
+          <t xml:space="preserve">仲間がいてくれたから、のびのびやれました。ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.easygoing[1]</t>
+          <t xml:space="preserve">defiant.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8133,14 +8133,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、何人来たか覚えてないです。でも、全部楽しかったですよ</t>
+          <t xml:space="preserve">MVPはありがたいですけど……やっぱり、みんなで勝ちたかったですね</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.easygoing[2]</t>
+          <t xml:space="preserve">defiant.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8165,14 +8165,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足がふらふらしてますけど……全員倒したから、まあいっかって感じです</t>
+          <t xml:space="preserve">次は三人揃って笑えるように。そう思ってます</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8182,12 +8182,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">gauntlet.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8197,14 +8197,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で行きます！ よろしくお願いします！</t>
+          <t xml:space="preserve">あはは、何人来たか覚えてないです。でも、全部楽しかったですよ</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">gauntlet.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8229,14 +8229,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった、勝ちました!最高の舞台で最高の結果、夢みたいです!</t>
+          <t xml:space="preserve">足がふらふらしてますけど……全員倒したから、まあいっかって感じです</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
@@ -8261,14 +8261,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました！ うちの団体の底力を見せられましたね！</t>
+          <t xml:space="preserve">全力で行きます！ よろしくお願いします！</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.polite.easygoing[1]</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8278,29 +8278,29 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後まで楽しかったです！ ありがとうございました！</t>
+          <t xml:space="preserve">やった、勝ちました！最高の舞台で最高の結果、夢みたいです！</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
@@ -8320,49 +8320,113 @@
       </c>
       <c r="E250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリー生活、今日で終わりです！助かりました</t>
+          <t xml:space="preserve">勝ちました！ うちの団体の底力を見せられましたね！</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後まで楽しかったです！ ありがとうございました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="40" customHeight="1">
+      <c r="A252" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">フリー生活は今日で卒業です！　ここから楽しくなりそう！</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="40" customHeight="1">
+      <c r="A253" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.polite.easygoing[1]</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr" s="2">
+      <c r="B253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr" s="12">
+      <c r="D253" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr" s="2">
+      <c r="E253" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">見つけてくださって助かりました！暴れますね</t>
+      <c r="F253" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">声をかけてくださって嬉しいです！　思いきり暴れますね！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H251"/>
+  <autoFilter ref="A1:H253"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×お気楽.xlsx
@@ -306,7 +306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3532,7 +3532,7 @@
     <row r="101" ht="40" customHeight="1">
       <c r="A101" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B101" t="inlineStr" s="2">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="D101" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_accept.polite.easygoing[1]</t>
+          <t xml:space="preserve">decline_accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr" s="2">
@@ -3557,14 +3557,14 @@
       </c>
       <c r="F101" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わあ、ありがとうございます！ さすが社長です！ 今年も楽しくやらせてくださいね！</t>
+          <t xml:space="preserve">オッケーです！ いやー、来年は上げてもらえるように頑張りますね！ お昼のおかず、一品減らします！</t>
         </is>
       </c>
     </row>
     <row r="102" ht="40" customHeight="1">
       <c r="A102" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_hold.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B102" t="inlineStr" s="2">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="D102" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_accept.polite.easygoing[1]</t>
+          <t xml:space="preserve">decline_hold.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E102" t="inlineStr" s="2">
@@ -3589,14 +3589,14 @@
       </c>
       <c r="F102" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">んー、まあいいです！ いただけるだけありがたいということで！</t>
+          <t xml:space="preserve">据え置き！？ やった、ありがとうございます！ ……あっ、これ、お礼に何かしないとまずいやつですね！？</t>
         </is>
       </c>
     </row>
     <row r="103" ht="40" customHeight="1">
       <c r="A103" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_open.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B103" t="inlineStr" s="2">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="D103" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_negotiate_refuse.polite.easygoing[1]</t>
+          <t xml:space="preserve">decline_open.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr" s="2">
@@ -3621,14 +3621,14 @@
       </c>
       <c r="F103" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あちゃー、だめですかー。まあ仕方ないですよね。……ちょっとへこみますけど。</t>
+          <t xml:space="preserve">えっ、下がっちゃうんですか！？ わっ、びっくりした……。うーん、まあ、そういう年もありますよね！</t>
         </is>
       </c>
     </row>
     <row r="104" ht="40" customHeight="1">
       <c r="A104" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_strict.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B104" t="inlineStr" s="2">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="D104" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_open.polite.easygoing[1]</t>
+          <t xml:space="preserve">decline_strict.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E104" t="inlineStr" s="2">
@@ -3653,14 +3653,14 @@
       </c>
       <c r="F104" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます！ 前向きに考えます！</t>
+          <t xml:space="preserve">うーん、さすがにちょっと堪えますね。……大丈夫です、明日には忘れてますから！</t>
         </is>
       </c>
     </row>
     <row r="105" ht="40" customHeight="1">
       <c r="A105" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B105" t="inlineStr" s="2">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="D105" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">raise_refuse.polite.easygoing[1]</t>
+          <t xml:space="preserve">decline_voluntary_accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E105" t="inlineStr" s="2">
@@ -3685,14 +3685,14 @@
       </c>
       <c r="F105" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、やっぱりですかー。まあ仕方ないですね。でもいつか上げてくださいね？ 約束ですよ？</t>
+          <t xml:space="preserve">はーい、決まりですね！ うん、なんかスッキリしました！ 身軽なほうが動けますし！</t>
         </is>
       </c>
     </row>
     <row r="106" ht="40" customHeight="1">
       <c r="A106" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_hold.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B106" t="inlineStr" s="2">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="D106" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.polite.easygoing[1]</t>
+          <t xml:space="preserve">decline_voluntary_hold.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E106" t="inlineStr" s="2">
@@ -3717,14 +3717,14 @@
       </c>
       <c r="F106" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー、ついにこの日が来てしまいましたね。では、お元気で。</t>
+          <t xml:space="preserve">えー！ 下げてって言ったのに！ ……もう、そういうの弱いんですから。ちゃんと働きます！</t>
         </is>
       </c>
     </row>
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.easygoing[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.decline_voluntary_open.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">sudden_departure.polite.easygoing[2]</t>
+          <t xml:space="preserve">decline_voluntary_open.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E107" t="inlineStr" s="2">
@@ -3749,14 +3749,14 @@
       </c>
       <c r="F107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もう潮時かなと思いまして。楽しかったですよ、ええ。失礼します！</t>
+          <t xml:space="preserve">社長、正直に言いますね！ 私、もうピークは過ぎました！ なので下げちゃってください、遠慮なく！</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_listen.polite.easygoing[1]</t>
+          <t xml:space="preserve">raise_accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E108" t="inlineStr" s="2">
@@ -3781,14 +3781,14 @@
       </c>
       <c r="F108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">聞いてくださるんですか？ うーん……{record}なんだかマンネリっていうか。新しいことがしたいんです。</t>
+          <t xml:space="preserve">わあ、ありがとうございます！ さすが社長です！ 今年も楽しくやらせてくださいね！</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.polite.easygoing[1]</t>
+          <t xml:space="preserve">raise_negotiate_accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E109" t="inlineStr" s="2">
@@ -3813,14 +3813,14 @@
       </c>
       <c r="F109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あのですね。{tenure}いろいろ考えたのですが……環境を変えてみたいなと思いまして。</t>
+          <t xml:space="preserve">んー、まあいいです！ いただけるだけありがたいということで！</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.easygoing[2]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_negotiate_refuse.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_open.polite.easygoing[2]</t>
+          <t xml:space="preserve">raise_negotiate_refuse.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E110" t="inlineStr" s="2">
@@ -3845,14 +3845,14 @@
       </c>
       <c r="F110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いやー社長、言いにくいのですが。{tenure}少し外の空気を吸ってみたいんです。</t>
+          <t xml:space="preserve">あちゃー、だめですかー。まあ仕方ないですよね。……ちょっとへこみますけど。</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_open.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_release.polite.easygoing[1]</t>
+          <t xml:space="preserve">raise_open.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E111" t="inlineStr" s="2">
@@ -3877,14 +3877,14 @@
       </c>
       <c r="F111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、まあそうなりますよねー。{tenure_farewell}{rivalry}お元気でー！</t>
+          <t xml:space="preserve">ありがとうございます！ 前向きに考えます！</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.raise_refuse.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_fail.polite.easygoing[1]</t>
+          <t xml:space="preserve">raise_refuse.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E112" t="inlineStr" s="2">
@@ -3909,14 +3909,14 @@
       </c>
       <c r="F112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ごめんなさい社長……。お金の問題じゃないんです。もう心が決まってしまって。</t>
+          <t xml:space="preserve">あはは、やっぱりですかー。まあ仕方ないですね。でもいつか上げてくださいね？ 約束ですよ？</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">transfer_retain_success.polite.easygoing[1]</t>
+          <t xml:space="preserve">sudden_departure.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E113" t="inlineStr" s="2">
@@ -3941,14 +3941,14 @@
       </c>
       <c r="F113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、本当ですか？ そこまでしてくださるんですか？ ……じゃあ、もう少しいようかな！</t>
+          <t xml:space="preserve">いやー、ついにこの日が来てしまいましたね。では、お元気で。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES.start.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.sudden_departure.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">NEGOTIATE_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">start.polite.easygoing[1]</t>
+          <t xml:space="preserve">sudden_departure.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E114" t="inlineStr" s="2">
@@ -3973,14 +3973,14 @@
       </c>
       <c r="F114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">条件次第ですね。…聞かせてください！</t>
+          <t xml:space="preserve">もう潮時かなと思いまして。楽しかったですよ、ええ。失礼します！</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_listen.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3990,29 +3990,29 @@
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.polite.easygoing[1]</t>
+          <t xml:space="preserve">transfer_listen.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、私たちの子のこと、よろしければ思い出してあげてくださいね〜。</t>
+          <t xml:space="preserve">聞いてくださるんですか？ うーん……{record}なんだかマンネリっていうか。新しいことがしたいんです。</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -4022,29 +4022,29 @@
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.polite.easygoing[1]</t>
+          <t xml:space="preserve">transfer_open.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、次のメイン、よろしければ私たちでやらせていただけませんか〜。</t>
+          <t xml:space="preserve">社長、あのですね。{tenure}いろいろ考えたのですが……環境を変えてみたいなと思いまして。</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_open.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -4054,29 +4054,29 @@
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.polite.easygoing[1]</t>
+          <t xml:space="preserve">transfer_open.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、お給料のこと、よろしければ少しご検討いただけませんか〜。</t>
+          <t xml:space="preserve">いやー社長、言いにくいのですが。{tenure}少し外の空気を吸ってみたいんです。</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_release.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -4086,29 +4086,29 @@
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.polite.easygoing[1]</t>
+          <t xml:space="preserve">transfer_release.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、私たちの頑張り、よろしければ一度褒めていただけませんか〜。</t>
+          <t xml:space="preserve">あはは、まあそうなりますよねー。{tenure_farewell}{rivalry}お元気でー！</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_fail.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -4118,29 +4118,29 @@
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">transfer_retain_fail.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、ありがとうございます〜！ 社長にそう言ってもらえると本当に嬉しいです。</t>
+          <t xml:space="preserve">ごめんなさい社長……。お金の問題じゃないんです。もう心が決まってしまって。</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES.transfer_retain_success.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -4150,29 +4150,29 @@
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">CONTRACT_NEGOTIATION_LINES</t>
         </is>
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">transfer_retain_success.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ〜、そうですか〜。失礼しました〜。</t>
+          <t xml:space="preserve">え、本当ですか？ そこまでしてくださるんですか？ ……じゃあ、もう少しいようかな！</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">NEGOTIATE_LINES.start.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -4182,29 +4182,29 @@
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">F07_LINES</t>
+          <t xml:space="preserve">NEGOTIATE_LINES</t>
         </is>
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">start.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">07 派閥イベント</t>
+          <t xml:space="preserve">06 契約交渉</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅん、別の形ですか〜。ありがとうございます〜。</t>
+          <t xml:space="preserve">条件次第ですね。…聞かせてください！</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_ABSTRACT.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_ABSTRACT.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E122" t="inlineStr" s="2">
@@ -4229,14 +4229,14 @@
       </c>
       <c r="F122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、社長ありがとうございます〜。期待に応えますね！</t>
+          <t xml:space="preserve">社長、私たちの子のこと、よろしければ思い出してあげてくださいね〜。</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MAIN.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MAIN.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E123" t="inlineStr" s="2">
@@ -4261,14 +4261,14 @@
       </c>
       <c r="F123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ〜、そうですか〜。まあ仕方ないですね。</t>
+          <t xml:space="preserve">社長、次のメイン、よろしければ私たちでやらせていただけませんか〜。</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_MONEY.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_MONEY.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E124" t="inlineStr" s="2">
@@ -4293,14 +4293,14 @@
       </c>
       <c r="F124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅん、別の手ですか〜。ありがとうございます〜。</t>
+          <t xml:space="preserve">社長、お給料のこと、よろしければ少しご検討いただけませんか〜。</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.leaderDemand.DEMAND_RECOGNITION.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">leaderDemand.DEMAND_RECOGNITION.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E125" t="inlineStr" s="2">
@@ -4325,14 +4325,14 @@
       </c>
       <c r="F125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、社長ありがとうございます〜！ みんな喜びます！</t>
+          <t xml:space="preserve">社長、私たちの頑張り、よろしければ一度褒めていただけませんか〜。</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E126" t="inlineStr" s="2">
@@ -4357,14 +4357,14 @@
       </c>
       <c r="F126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ〜、そうですか〜。承知しました。</t>
+          <t xml:space="preserve">わ、ありがとうございます〜！ 社長にそう言ってもらえると本当に嬉しいです。</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E127" t="inlineStr" s="2">
@@ -4389,14 +4389,14 @@
       </c>
       <c r="F127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅん、別の形ですか〜。ありがとうございます〜。</t>
+          <t xml:space="preserve">えぇ〜、そうですか〜。失礼しました〜。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_ABSTRACT.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_ABSTRACT.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E128" t="inlineStr" s="2">
@@ -4421,14 +4421,14 @@
       </c>
       <c r="F128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、ありがとうございます〜！ 社長に褒めてもらえるなんて！</t>
+          <t xml:space="preserve">ふぅん、別の形ですか〜。ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E129" t="inlineStr" s="2">
@@ -4453,14 +4453,14 @@
       </c>
       <c r="F129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ〜、そうですか〜。失礼しました〜。</t>
+          <t xml:space="preserve">わ、社長ありがとうございます〜。期待に応えますね！</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E130" t="inlineStr" s="2">
@@ -4485,14 +4485,14 @@
       </c>
       <c r="F130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅん、別の形ですか〜。ありがとうございます〜。</t>
+          <t xml:space="preserve">えぇ〜、そうですか〜。まあ仕方ないですね。</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MAIN.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MAIN.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E131" t="inlineStr" s="2">
@@ -4517,14 +4517,14 @@
       </c>
       <c r="F131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">え、気にされてました〜？ ごめんなさい、次は誘いますね〜。</t>
+          <t xml:space="preserve">ふぅん、別の手ですか〜。ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -4539,7 +4539,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E132" t="inlineStr" s="2">
@@ -4549,14 +4549,14 @@
       </c>
       <c r="F132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます〜！ 楽しんできます〜。</t>
+          <t xml:space="preserve">わ、社長ありがとうございます〜！ みんな喜びます！</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E133" t="inlineStr" s="2">
@@ -4581,14 +4581,14 @@
       </c>
       <c r="F133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、配慮足りなかったですか〜。気をつけます〜。</t>
+          <t xml:space="preserve">えぇ〜、そうですか〜。承知しました。</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_MONEY.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -4603,7 +4603,7 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_MONEY.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E134" t="inlineStr" s="2">
@@ -4613,14 +4613,14 @@
       </c>
       <c r="F134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます〜。</t>
+          <t xml:space="preserve">ふぅん、別の形ですか〜。ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E135" t="inlineStr" s="2">
@@ -4645,14 +4645,14 @@
       </c>
       <c r="F135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ〜、お客さんノッてたじゃないですか〜。…はい、控えます〜。</t>
+          <t xml:space="preserve">わ、ありがとうございます〜！ 社長に褒めてもらえるなんて！</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E136" t="inlineStr" s="2">
@@ -4677,14 +4677,14 @@
       </c>
       <c r="F136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、社長わかってる〜！ 引き続きやらせていただきます〜。</t>
+          <t xml:space="preserve">えぇ〜、そうですか〜。失礼しました〜。</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.DEMAND_RECOGNITION.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.DEMAND_RECOGNITION.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E137" t="inlineStr" s="2">
@@ -4709,14 +4709,14 @@
       </c>
       <c r="F137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、ばれてました〜？ すみません、明日から出ます〜。</t>
+          <t xml:space="preserve">ふぅん、別の形ですか〜。ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E138" t="inlineStr" s="2">
@@ -4741,14 +4741,14 @@
       </c>
       <c r="F138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、助かります〜、社長ありがとうございます。</t>
+          <t xml:space="preserve">え、気にされてました〜？ ごめんなさい、次は誘いますね〜。</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BONDING.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BONDING.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E139" t="inlineStr" s="2">
@@ -4773,14 +4773,14 @@
       </c>
       <c r="F139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅん、メンバー優先ですか〜。それも助かります〜。</t>
+          <t xml:space="preserve">ありがとうございます〜！ 楽しんできます〜。</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E140" t="inlineStr" s="2">
@@ -4805,14 +4805,14 @@
       </c>
       <c r="F140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、見ててくれたんですか〜。じゃ、休ませていただきます〜。</t>
+          <t xml:space="preserve">あ、配慮足りなかったですか〜。気をつけます〜。</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_BOUNDARY.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_BOUNDARY.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E141" t="inlineStr" s="2">
@@ -4837,14 +4837,14 @@
       </c>
       <c r="F141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いや〜、まだいけます〜。</t>
+          <t xml:space="preserve">ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E142" t="inlineStr" s="2">
@@ -4869,14 +4869,14 @@
       </c>
       <c r="F142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お、メンバーケアですか〜。助かります〜。</t>
+          <t xml:space="preserve">えぇ〜、お客さんノッてたじゃないですか〜。…はい、控えます〜。</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.INCIDENT_HEEL_PROVOKE.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E143" t="inlineStr" s="2">
@@ -4901,14 +4901,14 @@
       </c>
       <c r="F143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ〜、そんな話あったんですか〜。注意しときます〜。</t>
+          <t xml:space="preserve">わ、社長わかってる〜！ 引き続きやらせていただきます〜。</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E144" t="inlineStr" s="2">
@@ -4933,14 +4933,14 @@
       </c>
       <c r="F144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ありがとうございます〜。穏便にいきますね。</t>
+          <t xml:space="preserve">あ、ばれてました〜？ すみません、明日から出ます〜。</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E145" t="inlineStr" s="2">
@@ -4965,14 +4965,14 @@
       </c>
       <c r="F145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅん、別ルートですか〜。下の子のケア、助かります〜。</t>
+          <t xml:space="preserve">わ、助かります〜、社長ありがとうございます。</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_ABSENCE.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_ABSENCE.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E146" t="inlineStr" s="2">
@@ -4997,14 +4997,14 @@
       </c>
       <c r="F146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、はい〜。気をつけさせていただきます。</t>
+          <t xml:space="preserve">ふぅん、メンバー優先ですか〜。それも助かります〜。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E147" t="inlineStr" s="2">
@@ -5029,14 +5029,14 @@
       </c>
       <c r="F147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">（曖昧に笑って、お辞儀した）</t>
+          <t xml:space="preserve">わ、見ててくれたんですか〜。じゃ、休ませていただきます〜。</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E148" t="inlineStr" s="2">
@@ -5061,14 +5061,14 @@
       </c>
       <c r="F148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふぅん、別ルートですか〜。ありがとうございます〜。</t>
+          <t xml:space="preserve">いや〜、まだいけます〜。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_FAN_PRESSURE.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_FAN_PRESSURE.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E149" t="inlineStr" s="2">
@@ -5093,14 +5093,14 @@
       </c>
       <c r="F149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えぇ〜、これくらい大丈夫だと思ったんですけど〜。緩めますね〜。</t>
+          <t xml:space="preserve">お、メンバーケアですか〜。助かります〜。</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E150" t="inlineStr" s="2">
@@ -5125,14 +5125,14 @@
       </c>
       <c r="F150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わ、続けていいんですか〜！ ありがとうございます〜。</t>
+          <t xml:space="preserve">えぇ〜、そんな話あったんですか〜。注意しときます〜。</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E151" t="inlineStr" s="2">
@@ -5157,14 +5157,14 @@
       </c>
       <c r="F151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ、私じゃなくて子たち優先ですか〜？ ありがたいです〜。</t>
+          <t xml:space="preserve">ありがとうございます〜。穏便にいきますね。</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.easygoing.attack.polite</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_INTERNAL_RANK.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -5174,12 +5174,12 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.attack.polite</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_INTERNAL_RANK.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E152" t="inlineStr" s="2">
@@ -5189,14 +5189,14 @@
       </c>
       <c r="F152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲良しはここまでですね！　さあ、本気でいきましょう！</t>
+          <t xml:space="preserve">ふぅん、別ルートですか〜。下の子のケア、助かります〜。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES.easygoing.defend.polite</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -5206,12 +5206,12 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FACTION_F02_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">easygoing.defend.polite</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E153" t="inlineStr" s="2">
@@ -5221,14 +5221,14 @@
       </c>
       <c r="F153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まあ、仕方ありませんね</t>
+          <t xml:space="preserve">あ、はい〜。気をつけさせていただきます。</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -5238,29 +5238,29 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">なんか最近調子いいんです！ もっと上に行けそうです！</t>
+          <t xml:space="preserve">（曖昧に笑って、お辞儀した）</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_RIVAL_HEAT.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -5270,29 +5270,29 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_RIVAL_HEAT.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近ちょっとモチベーションが…でも頑張ります</t>
+          <t xml:space="preserve">ふぅん、別ルートですか〜。ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -5302,29 +5302,29 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.A.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やる気出てきました！ もう大丈夫です！</t>
+          <t xml:space="preserve">えぇ〜、これくらい大丈夫だと思ったんですけど〜。緩めますね〜。</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -5334,29 +5334,29 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_END_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.B.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">調子戻ってきました！ もう大丈夫です！</t>
+          <t xml:space="preserve">わ、続けていいんですか〜！ ありがとうございます〜。</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES.defeat.polite.easygoing[1]</t>
+          <t xml:space="preserve">F07_LINES.resultLeader.OBSERVE_TRAINING_HARD.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -5366,29 +5366,29 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SLUMP_START_LINES</t>
+          <t xml:space="preserve">F07_LINES</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defeat.polite.easygoing[1]</t>
+          <t xml:space="preserve">resultLeader.OBSERVE_TRAINING_HARD.C.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最近ちょっと調子悪くて…でも大丈夫です！</t>
+          <t xml:space="preserve">あれ、私じゃなくて子たち優先ですか〜？ ありがたいです〜。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.polite.easygoing[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.attack.polite</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -5398,29 +5398,29 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">autumnWarChampion.polite.easygoing[1]</t>
+          <t xml:space="preserve">easygoing.attack.polite</t>
         </is>
       </c>
       <c r="E159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなと一緒に喜べる優勝って、最高ですね。</t>
+          <t xml:space="preserve">仲良しはここまでですね！　さあ、本気でいきましょう！</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.easygoing[1]</t>
+          <t xml:space="preserve">FACTION_F02_LINES.easygoing.defend.polite</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -5430,29 +5430,29 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">FACTION_F02_LINES</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bestMatch.polite.easygoing[1]</t>
+          <t xml:space="preserve">easygoing.defend.polite</t>
         </is>
       </c>
       <c r="E160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">07 派閥イベント</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の試合でした！ 相手にも感謝です！</t>
+          <t xml:space="preserve">まあ、仕方ありませんね</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.champion.polite.easygoing[1]</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -5462,29 +5462,29 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">BREAKTHROUGH_LINES</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一年間守り抜きました！ 来年も頑張ります！</t>
+          <t xml:space="preserve">なんか最近調子いいんです！ もっと上に行けそうです！</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.easygoing[1]</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -5494,29 +5494,29 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_LOSS_LINES</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hallOfFame.polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">殿堂入りですか…！ 信じられません…ありがとうございます！</t>
+          <t xml:space="preserve">最近ちょっとモチベーションが…でも頑張ります</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.mvp.polite.easygoing[1]</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -5526,29 +5526,29 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">MOTIVATION_RECOVERY_LINES</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">mvp.polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPですか！ ありがとうございます！ 来年も頑張ります！</t>
+          <t xml:space="preserve">やる気出てきました！ もう大丈夫です！</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.rookie.polite.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_END_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -5558,29 +5558,29 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_END_LINES</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rookie.polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">うそです…！ 新人王ですか…！ ありがとうございます！</t>
+          <t xml:space="preserve">調子戻ってきました！ もう大丈夫です！</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AWARD_LINES.springTagChampion.polite.easygoing[1]</t>
+          <t xml:space="preserve">SLUMP_START_LINES.defeat.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -5590,29 +5590,29 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AWARD_LINES</t>
+          <t xml:space="preserve">SLUMP_START_LINES</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">springTagChampion.polite.easygoing[1]</t>
+          <t xml:space="preserve">defeat.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
+          <t xml:space="preserve">08 成長・スランプ・モチベーション</t>
         </is>
       </c>
       <c r="F165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相棒と優勝できて、本当にうれしいです。</t>
+          <t xml:space="preserve">最近ちょっと調子悪くて…でも大丈夫です！</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.autumnWarChampion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">autumnWarChampion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E166" t="inlineStr" s="2">
@@ -5637,14 +5637,14 @@
       </c>
       <c r="F166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ドーム、嬉しいですね。気負わずいきましょう</t>
+          <t xml:space="preserve">みんなと一緒に喜べる優勝って、最高ですね。</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.bestMatch.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[2]</t>
+          <t xml:space="preserve">bestMatch.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr" s="2">
@@ -5669,14 +5669,14 @@
       </c>
       <c r="F167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">お客様と一緒に楽しい時間を作れたら</t>
+          <t xml:space="preserve">最高の試合でした！ 相手にも感謝です！</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.easygoing[3]</t>
+          <t xml:space="preserve">AWARD_LINES.champion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[3]</t>
+          <t xml:space="preserve">champion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr" s="2">
@@ -5701,14 +5701,14 @@
       </c>
       <c r="F168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ゆったり構えて、精一杯やります</t>
+          <t xml:space="preserve">一年間守り抜きました！ 来年も頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.hallOfFame.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -5718,12 +5718,12 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">hallOfFame.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr" s="2">
@@ -5733,14 +5733,14 @@
       </c>
       <c r="F169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">満員、嬉しいですね。本当に感謝です</t>
+          <t xml:space="preserve">殿堂入りですか…！ 信じられません…ありがとうございます！</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">AWARD_LINES.mvp.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5750,12 +5750,12 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[2]</t>
+          <t xml:space="preserve">mvp.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr" s="2">
@@ -5765,14 +5765,14 @@
       </c>
       <c r="F170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みなさんが来てくれたおかげですね</t>
+          <t xml:space="preserve">MVPですか！ ありがとうございます！ 来年も頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.easygoing[3]</t>
+          <t xml:space="preserve">AWARD_LINES.rookie.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[3]</t>
+          <t xml:space="preserve">rookie.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr" s="2">
@@ -5797,14 +5797,14 @@
       </c>
       <c r="F171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ゆったりと喜びを噛みしめます</t>
+          <t xml:space="preserve">うそです…！ 新人王ですか…！ ありがとうございます！</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.easygoing[1]</t>
+          <t xml:space="preserve">AWARD_LINES.springTagChampion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5814,29 +5814,29 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">AWARD_LINES</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.polite.easygoing[1]</t>
+          <t xml:space="preserve">springTagChampion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">もっと多くの方に見ていただきたくて…出させていただけませんか</t>
+          <t xml:space="preserve">相棒と優勝できて、本当にうれしいです。</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.easygoing[2]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5846,29 +5846,29 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.polite.easygoing[2]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">テレビ、ですか…！ぜひ、出させてください！</t>
+          <t xml:space="preserve">ドーム、嬉しいですね。気負わずいきましょう</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.polite.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5878,29 +5878,29 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">E1.accept.polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やったー！信じられない、夢みたい……！</t>
+          <t xml:space="preserve">お客様と一緒に楽しい時間を作れたら</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES.polite.easygoing[3]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5910,29 +5910,29 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">DOME_FIRSTSHOW_LINES</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[3]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ、一緒に楽しくやりましょう</t>
+          <t xml:space="preserve">ゆったり構えて、精一杯やります</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5942,29 +5942,29 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[2]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈なプロレスはしないって約束します</t>
+          <t xml:space="preserve">満員、嬉しいですね。本当に感謝です</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5974,29 +5974,29 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いしますね〜 楽しみです</t>
+          <t xml:space="preserve">みなさんが来てくれたおかげですね</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES.polite.easygoing[3]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -6006,29 +6006,29 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">DOME_SELLOUT_LINES</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[3]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">09 表彰式・記録・ドーム到達</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっほー、新天地です！暴れまくりますよ</t>
+          <t xml:space="preserve">ゆったりと喜びを噛みしめます</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -6038,29 +6038,29 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[2]</t>
+          <t xml:space="preserve">E1.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここなら好き放題やれそうです。楽しみ</t>
+          <t xml:space="preserve">もっと多くの方に見ていただきたくて…出させていただけませんか</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES.E1.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -6070,29 +6070,29 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_DIALOGUES</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">E1.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わーい、今日から仲間です！よろしくお願いします</t>
+          <t xml:space="preserve">テレビ、ですか…！ぜひ、出させてください！</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES.E1.accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -6102,29 +6102,29 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
+          <t xml:space="preserve">CHOICE_EVENT_RESULT_DIALOGUES</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[2]</t>
+          <t xml:space="preserve">E1.accept.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">12 選手経歴イベント</t>
+          <t xml:space="preserve">11 選択イベント・大型イベント・社長室</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで楽しくやりましょう</t>
+          <t xml:space="preserve">やったー！信じられない、夢みたい……！</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_INJURY_LINES</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
@@ -6149,14 +6149,14 @@
       </c>
       <c r="F182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、ちょっと休みますね〜 すぐ戻ります</t>
+          <t xml:space="preserve">えへへ、一緒に楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_INTEREST_LINES</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr" s="2">
@@ -6181,14 +6181,14 @@
       </c>
       <c r="F183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">えへへ、一緒に楽しくやりましょう</t>
+          <t xml:space="preserve">退屈なプロレスはしないって約束します</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_DRAFT_JOIN_LINES</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftInterest.polite.easygoing[2]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr" s="2">
@@ -6213,14 +6213,14 @@
       </c>
       <c r="F184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">退屈なプロレスはしないって約束します</t>
+          <t xml:space="preserve">よろしくお願いしますね〜 楽しみです</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -6230,12 +6230,12 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">draftJoin.polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr" s="2">
@@ -6245,14 +6245,14 @@
       </c>
       <c r="F185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">よろしくお願いしますね〜 楽しみです</t>
+          <t xml:space="preserve">やっほー、新天地です！暴れまくりますよ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_SIGNING_LINES</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faGreeting.polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr" s="2">
@@ -6277,14 +6277,14 @@
       </c>
       <c r="F186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリー生活は今日で卒業です！　ここから楽しくなりそう！</t>
+          <t xml:space="preserve">ここなら好き放題やれそうです。楽しみ</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr" s="2">
@@ -6309,14 +6309,14 @@
       </c>
       <c r="F187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やっほー、新天地です！暴れまくりますよ</t>
+          <t xml:space="preserve">わーい、今日から仲間です！よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_FA_WELCOME_LINES</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faSigning.polite.easygoing[2]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr" s="2">
@@ -6341,14 +6341,14 @@
       </c>
       <c r="F188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここなら好き放題やれそうです。楽しみ</t>
+          <t xml:space="preserve">みんなで楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
+          <t xml:space="preserve">EVENT_INJURY_LINES</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr" s="2">
@@ -6373,14 +6373,14 @@
       </c>
       <c r="F189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">わーい、今日から仲間です！よろしくお願いします</t>
+          <t xml:space="preserve">あ、ちょっと休みますね〜 すぐ戻ります</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faWelcome.polite.easygoing[2]</t>
+          <t xml:space="preserve">draftInterest.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr" s="2">
@@ -6405,14 +6405,14 @@
       </c>
       <c r="F190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">みんなで楽しくやりましょう</t>
+          <t xml:space="preserve">えへへ、一緒に楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftInterest.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">injury.polite.easygoing[1]</t>
+          <t xml:space="preserve">draftInterest.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr" s="2">
@@ -6437,14 +6437,14 @@
       </c>
       <c r="F191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あ、ちょっと休みますね〜 すぐ戻ります</t>
+          <t xml:space="preserve">退屈なプロレスはしないって約束します</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.draftJoin.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">release.polite.easygoing[1]</t>
+          <t xml:space="preserve">draftJoin.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr" s="2">
@@ -6469,14 +6469,14 @@
       </c>
       <c r="F192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、ご縁がなかったですね〜 ありがとうございました</t>
+          <t xml:space="preserve">よろしくお願いしますね〜 楽しみです</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.polite.easygoing[1]</t>
+          <t xml:space="preserve">faGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr" s="2">
@@ -6501,14 +6501,14 @@
       </c>
       <c r="F193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おじゃましまーす！短い間ですけど暴れますよ</t>
+          <t xml:space="preserve">フリー生活は今日で卒業です！　ここから楽しくなりそう！</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rentalGreeting.polite.easygoing[2]</t>
+          <t xml:space="preserve">faSigning.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr" s="2">
@@ -6533,14 +6533,14 @@
       </c>
       <c r="F194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一時的だからこそ、思い切り好き放題やりますね</t>
+          <t xml:space="preserve">やっほー、新天地です！暴れまくりますよ</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faSigning.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">scoutGreeting.polite.easygoing[1]</t>
+          <t xml:space="preserve">faSigning.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr" s="2">
@@ -6565,14 +6565,14 @@
       </c>
       <c r="F195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声をかけてくださって嬉しいです！　思いきり暴れますね！</t>
+          <t xml:space="preserve">ここなら好き放題やれそうです。楽しみ</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.polite.easygoing[1]</t>
+          <t xml:space="preserve">faWelcome.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr" s="2">
@@ -6597,14 +6597,14 @@
       </c>
       <c r="F196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けちゃいましたけど…次はもっといい試合をします</t>
+          <t xml:space="preserve">わーい、今日から仲間です！よろしくお願いします</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.faWelcome.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleChallengeLoss.polite.easygoing[2]</t>
+          <t xml:space="preserve">faWelcome.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E197" t="inlineStr" s="2">
@@ -6629,14 +6629,14 @@
       </c>
       <c r="F197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですけど、下を向いてたら応援してくれる人に失礼ですもんね</t>
+          <t xml:space="preserve">みんなで楽しくやりましょう</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.injury.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.polite.easygoing[1]</t>
+          <t xml:space="preserve">injury.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr" s="2">
@@ -6661,14 +6661,14 @@
       </c>
       <c r="F198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンは私です。また守り切りました</t>
+          <t xml:space="preserve">あ、ちょっと休みますね〜 すぐ戻ります</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.release.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleDefense.polite.easygoing[2]</t>
+          <t xml:space="preserve">release.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr" s="2">
@@ -6693,14 +6693,14 @@
       </c>
       <c r="F199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合でした。また挑戦してきてくださいね</t>
+          <t xml:space="preserve">あはは、ご縁がなかったですね〜 ありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.polite.easygoing[1]</t>
+          <t xml:space="preserve">rentalGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr" s="2">
@@ -6725,14 +6725,14 @@
       </c>
       <c r="F200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃいました…でもファンが応援してくれる限り、立ち上がります</t>
+          <t xml:space="preserve">おじゃましまーす！短い間ですけど暴れますよ</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.rentalGreeting.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleLoss.polite.easygoing[2]</t>
+          <t xml:space="preserve">rentalGreeting.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr" s="2">
@@ -6757,14 +6757,14 @@
       </c>
       <c r="F201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトのない自分なんて想像できませんでした。でも、私は私ですから</t>
+          <t xml:space="preserve">一時的だからこそ、思い切り好き放題やりますね</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.scoutGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.polite.easygoing[1]</t>
+          <t xml:space="preserve">scoutGreeting.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr" s="2">
@@ -6789,14 +6789,14 @@
       </c>
       <c r="F202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新チャンピオン誕生です。これからもっと盛り上げます</t>
+          <t xml:space="preserve">声をかけてくださって嬉しいです！　思いきり暴れますね！</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">titleWin.polite.easygoing[2]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr" s="2">
@@ -6821,14 +6821,14 @@
       </c>
       <c r="F203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト獲っちゃいました。最高です</t>
+          <t xml:space="preserve">今日は負けちゃいましたけど…次はもっといい試合をします</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleChallengeLoss.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">titleChallengeLoss.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr" s="2">
@@ -6853,14 +6853,14 @@
       </c>
       <c r="F204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、ご縁がなかったですね〜 ありがとうございました</t>
+          <t xml:space="preserve">悔しいですけど、下を向いてたら応援してくれる人に失礼ですもんね</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">titleDefense.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr" s="2">
@@ -6885,14 +6885,14 @@
       </c>
       <c r="F205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">おじゃましまーす！短い間ですけど暴れますよ</t>
+          <t xml:space="preserve">チャンピオンは私です。また守り切りました</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleDefense.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[2]</t>
+          <t xml:space="preserve">titleDefense.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr" s="2">
@@ -6917,14 +6917,14 @@
       </c>
       <c r="F206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一時的だからこそ、思い切り好き放題やりますね</t>
+          <t xml:space="preserve">いい試合でした。また挑戦してきてくださいね</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">titleLoss.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr" s="2">
@@ -6949,14 +6949,14 @@
       </c>
       <c r="F207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今日は負けちゃいましたけど…次はもっといい試合をします</t>
+          <t xml:space="preserve">負けちゃいました…でもファンが応援してくれる限り、立ち上がります</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleLoss.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[2]</t>
+          <t xml:space="preserve">titleLoss.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr" s="2">
@@ -6981,14 +6981,14 @@
       </c>
       <c r="F208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">悔しいですけど、下を向いてたら応援してくれる人に失礼ですもんね</t>
+          <t xml:space="preserve">…ベルトのない自分なんて想像できませんでした。でも、私は私ですから</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">titleWin.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr" s="2">
@@ -7013,14 +7013,14 @@
       </c>
       <c r="F209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">チャンピオンは私です。また守り切りました</t>
+          <t xml:space="preserve">新チャンピオン誕生です。これからもっと盛り上げます</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY.titleWin.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
+          <t xml:space="preserve">EVENT_LINES_BY_KEY</t>
         </is>
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[2]</t>
+          <t xml:space="preserve">titleWin.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr" s="2">
@@ -7045,14 +7045,14 @@
       </c>
       <c r="F210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい試合でした。また挑戦してきてくださいね</t>
+          <t xml:space="preserve">ベルト獲っちゃいました。最高です</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -7062,7 +7062,7 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RELEASE_LINES</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
@@ -7077,14 +7077,14 @@
       </c>
       <c r="F211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">負けちゃいました…でもファンが応援してくれる限り、立ち上がります</t>
+          <t xml:space="preserve">あはは、ご縁がなかったですね〜 ありがとうございました</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -7094,12 +7094,12 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[2]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr" s="2">
@@ -7109,14 +7109,14 @@
       </c>
       <c r="F212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ベルトのない自分なんて想像できませんでした。でも、私は私ですから</t>
+          <t xml:space="preserve">おじゃましまーす！短い間ですけど暴れますよ</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_RENTAL_GREETING_LINES</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr" s="2">
@@ -7141,14 +7141,14 @@
       </c>
       <c r="F213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新チャンピオン誕生です。これからもっと盛り上げます</t>
+          <t xml:space="preserve">一時的だからこそ、思い切り好き放題やりますね</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.easygoing[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[2]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr" s="2">
@@ -7173,14 +7173,14 @@
       </c>
       <c r="F214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ベルト獲っちゃいました。最高です</t>
+          <t xml:space="preserve">今日は負けちゃいましたけど…次はもっといい試合をします</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -7190,29 +7190,29 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_CHALLENGE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_39_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、ちょっと合わないかもしれません…</t>
+          <t xml:space="preserve">悔しいですけど、下を向いてたら応援してくれる人に失礼ですもんね</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -7222,29 +7222,29 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あれ〜、最近ちょっと素っ気ないような…</t>
+          <t xml:space="preserve">チャンピオンは私です。また守り切りました</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -7254,29 +7254,29 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_DEFENSE_LINES</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_59_down.easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ん〜、なんだか少し空気が変わりましたかね〜</t>
+          <t xml:space="preserve">いい試合でした。また挑戦してきてくださいね</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -7286,29 +7286,29 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_60_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気楽にお付き合いできて嬉しいです〜</t>
+          <t xml:space="preserve">負けちゃいました…でもファンが応援してくれる限り、立ち上がります</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -7318,29 +7318,29 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_LOSS_LINES</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高の相棒です〜。ずっと一緒にいたいですね</t>
+          <t xml:space="preserve">…ベルトのない自分なんて想像できませんでした。でも、私は私ですから</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -7350,29 +7350,29 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bond_80_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一緒だと、何もかも上手くいく気がするんです</t>
+          <t xml:space="preserve">新チャンピオン誕生です。これからもっと盛り上げます</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -7382,29 +7382,29 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES</t>
+          <t xml:space="preserve">EVENT_TITLE_WIN_LINES</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.polite[1]</t>
+          <t xml:space="preserve">polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
+          <t xml:space="preserve">12 選手経歴イベント</t>
         </is>
       </c>
       <c r="F221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">熱い関係も一段落ですね。ちょっと寂しいです</t>
+          <t xml:space="preserve">ベルト獲っちゃいました。最高です</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_39_down.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_29_down.easygoing.polite[2]</t>
+          <t xml:space="preserve">bond_39_down.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr" s="2">
@@ -7429,14 +7429,14 @@
       </c>
       <c r="F222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ因縁も永遠じゃありませんよね〜</t>
+          <t xml:space="preserve">う〜ん、ちょっと合わないかもしれません…</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E223" t="inlineStr" s="2">
@@ -7461,14 +7461,14 @@
       </c>
       <c r="F223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">いい勝負になりそうですね〜。燃えてきました</t>
+          <t xml:space="preserve">あれ〜、最近ちょっと素っ気ないような…</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_59_down.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_30_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">bond_59_down.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E224" t="inlineStr" s="2">
@@ -7493,14 +7493,14 @@
       </c>
       <c r="F224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、負けたくないです〜</t>
+          <t xml:space="preserve">ん〜、なんだか少し空気が変わりましたかね〜</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_60_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">bond_60_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr" s="2">
@@ -7525,14 +7525,14 @@
       </c>
       <c r="F225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本気でやり合いたい相手なんて、そういませんよ〜</t>
+          <t xml:space="preserve">気楽にお付き合いできて嬉しいです〜</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_50_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr" s="2">
@@ -7557,14 +7557,14 @@
       </c>
       <c r="F226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふふ、考えると自然と気合が入ります</t>
+          <t xml:space="preserve">最高の相棒です〜。ずっと一緒にいたいですね</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.bond_80_up.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.polite[1]</t>
+          <t xml:space="preserve">bond_80_up.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr" s="2">
@@ -7589,14 +7589,14 @@
       </c>
       <c r="F227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この試合が一番楽しいんです。ずっとこの関係が続けばいいのに</t>
+          <t xml:space="preserve">一緒だと、何もかも上手くいく気がするんです</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalry_70_up.easygoing.polite[2]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr" s="2">
@@ -7621,14 +7621,14 @@
       </c>
       <c r="F228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">運命のライバルですね〜。最高です</t>
+          <t xml:space="preserve">熱い関係も一段落ですね。ちょっと寂しいです</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_29_down.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.polite[1]</t>
+          <t xml:space="preserve">rivalry_29_down.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E229" t="inlineStr" s="2">
@@ -7653,14 +7653,14 @@
       </c>
       <c r="F229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここ最高です〜！ みんなとやるの楽しいです！</t>
+          <t xml:space="preserve">まぁ因縁も永遠じゃありませんよね〜</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_above_75.easygoing.polite[2]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr" s="2">
@@ -7685,14 +7685,14 @@
       </c>
       <c r="F230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">この団体、すっごく居心地いいんですよね〜</t>
+          <t xml:space="preserve">いい勝負になりそうですね〜。燃えてきました</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_30_up.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.polite[1]</t>
+          <t xml:space="preserve">rivalry_30_up.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr" s="2">
@@ -7717,14 +7717,14 @@
       </c>
       <c r="F231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">さすがにこれは…笑えないですね</t>
+          <t xml:space="preserve">あはは、負けたくないです〜</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -7739,7 +7739,7 @@
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_20.easygoing.polite[2]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr" s="2">
@@ -7749,14 +7749,14 @@
       </c>
       <c r="F232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは…なんて笑っている場合じゃないですよね、これ</t>
+          <t xml:space="preserve">本気でやり合いたい相手なんて、そういませんよ〜</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.polite[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_50_up.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.polite[1]</t>
+          <t xml:space="preserve">rivalry_50_up.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr" s="2">
@@ -7781,14 +7781,14 @@
       </c>
       <c r="F233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">う〜ん、最近ちょっとモヤモヤします…</t>
+          <t xml:space="preserve">ふふ、考えると自然と気合が入ります</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.polite[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trust_below_35.easygoing.polite[2]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr" s="2">
@@ -7813,14 +7813,14 @@
       </c>
       <c r="F234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">まぁ大丈夫…ですよね？ ちょっと不安ですけど</t>
+          <t xml:space="preserve">この試合が一番楽しいんです。ずっとこの関係が続けばいいのに</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.rivalry_70_up.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">rivalry_70_up.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr" s="2">
@@ -7845,14 +7845,14 @@
       </c>
       <c r="F235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">連勝ストップかあ…でもまた頑張ります！</t>
+          <t xml:space="preserve">運命のライバルですね〜。最高です</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -7862,29 +7862,29 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.easygoing[1]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、身体はもうへとへとです。でも、最後まで頑張りますよ</t>
+          <t xml:space="preserve">ここ最高です〜！ みんなとやるの楽しいです！</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_above_75.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -7894,29 +7894,29 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preFinal.polite.easygoing[2]</t>
+          <t xml:space="preserve">trust_above_75.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ここまで来たら、やるしかないですよね。痛いけど、まあいっか</t>
+          <t xml:space="preserve">この団体、すっごく居心地いいんですよね〜</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -7926,29 +7926,29 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相手の方ですね。えーと、気楽に…いや、ちゃんとやります</t>
+          <t xml:space="preserve">さすがにこれは…笑えないですね</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_20.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -7958,29 +7958,29 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">preMatch.polite.easygoing[2]</t>
+          <t xml:space="preserve">trust_below_20.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一戦ずつ、しっかりお相手しますよ。ま、任せてください</t>
+          <t xml:space="preserve">あはは…なんて笑っている場合じゃないですよね、これ</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7990,29 +7990,29 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.easygoing[1]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.polite[1]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">一人、倒せました。…はぁ、疲れましたけど、まだ退けません。次の方、どうぞ</t>
+          <t xml:space="preserve">う〜ん、最近ちょっとモヤモヤします…</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.easygoing[2]</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES.trust_below_35.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -8022,29 +8022,29 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
+          <t xml:space="preserve">GLIMPSE_A_LINES</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">survivor.polite.easygoing[2]</t>
+          <t xml:space="preserve">trust_below_35.easygoing.polite[2]</t>
         </is>
       </c>
       <c r="E241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふう、一人おしまいです。でも、まだ立ってますよ。次、来てくださいねー</t>
+          <t xml:space="preserve">まぁ大丈夫…ですよね？ ちょっと不安ですけど</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.easygoing[1]</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -8054,29 +8054,29 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">GLIMPSE_HOTSTREAK_END_LINES</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.easygoing[1]</t>
+          <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+          <t xml:space="preserve">13 Glimpse Cascade(興行後の一言)</t>
         </is>
       </c>
       <c r="F242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最高のチームでしたよね。三人で勝てて、本当に嬉しいです</t>
+          <t xml:space="preserve">連勝ストップかあ…でもまた頑張ります！</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">champion.polite.easygoing[2]</t>
+          <t xml:space="preserve">preFinal.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E243" t="inlineStr" s="2">
@@ -8101,14 +8101,14 @@
       </c>
       <c r="F243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">仲間がいてくれたから、のびのびやれました。ありがとうございます</t>
+          <t xml:space="preserve">あはは、身体はもうへとへとです。でも、最後まで頑張りますよ</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preFinal.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.easygoing[1]</t>
+          <t xml:space="preserve">preFinal.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr" s="2">
@@ -8133,14 +8133,14 @@
       </c>
       <c r="F244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">MVPはありがたいですけど……やっぱり、みんなで勝ちたかったですね</t>
+          <t xml:space="preserve">ここまで来たら、やるしかないですよね。痛いけど、まあいっか</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">defiant.polite.easygoing[2]</t>
+          <t xml:space="preserve">preMatch.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr" s="2">
@@ -8165,14 +8165,14 @@
       </c>
       <c r="F245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">次は三人揃って笑えるように。そう思ってます</t>
+          <t xml:space="preserve">相手の方ですね。えーと、気楽に…いや、ちゃんとやります</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.preMatch.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -8182,12 +8182,12 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.easygoing[1]</t>
+          <t xml:space="preserve">preMatch.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr" s="2">
@@ -8197,14 +8197,14 @@
       </c>
       <c r="F246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あはは、何人来たか覚えてないです。でも、全部楽しかったですよ</t>
+          <t xml:space="preserve">一戦ずつ、しっかりお相手しますよ。ま、任せてください</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.easygoing[2]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">gauntlet.polite.easygoing[2]</t>
+          <t xml:space="preserve">survivor.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr" s="2">
@@ -8229,14 +8229,14 @@
       </c>
       <c r="F247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">足がふらふらしてますけど……全員倒したから、まあいっかって感じです</t>
+          <t xml:space="preserve">一人、倒せました。…はぁ、疲れましたけど、まだ退けません。次の方、どうぞ</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES.survivor.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MATCH_LINES</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">survivor.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr" s="2">
@@ -8261,14 +8261,14 @@
       </c>
       <c r="F248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全力で行きます！ よろしくお願いします！</t>
+          <t xml:space="preserve">ふう、一人おしまいです。でも、まだ立ってますよ。次、来てくださいねー</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">champion.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr" s="2">
@@ -8293,14 +8293,14 @@
       </c>
       <c r="F249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">やった、勝ちました！最高の舞台で最高の結果、夢みたいです！</t>
+          <t xml:space="preserve">最高のチームでしたよね。三人で勝てて、本当に嬉しいです</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.champion.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">champion.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr" s="2">
@@ -8325,14 +8325,14 @@
       </c>
       <c r="F250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝ちました！ うちの団体の底力を見せられましたね！</t>
+          <t xml:space="preserve">仲間がいてくれたから、のびのびやれました。ありがとうございます</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">ENDING_LINES.fighter.polite.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -8342,29 +8342,29 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">ENDING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">fighter.polite.easygoing[1]</t>
+          <t xml:space="preserve">defiant.polite.easygoing[1]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">18 経営危機・エンディング</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">最後まで楽しかったです！ ありがとうございました！</t>
+          <t xml:space="preserve">MVPはありがたいですけど……やっぱり、みんなで勝ちたかったですね</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES.polite.easygoing[1]</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.defiant.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -8374,59 +8374,283 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">FA_GREETING_LINES</t>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">polite.easygoing[1]</t>
+          <t xml:space="preserve">defiant.polite.easygoing[2]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">19 ドラフト・スカウト</t>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
         </is>
       </c>
       <c r="F252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">フリー生活は今日で卒業です！　ここから楽しくなりそう！</t>
+          <t xml:space="preserve">次は三人揃って笑えるように。そう思ってます</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">あはは、何人来たか覚えてないです。でも、全部楽しかったですよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="40" customHeight="1">
+      <c r="A254" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES.gauntlet.polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AUTUMN_WAR_MVP_LINES</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">gauntlet.polite.easygoing[2]</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">足がふらふらしてますけど……全員倒したから、まあいっかって感じです</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="40" customHeight="1">
+      <c r="A255" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_OPPONENT_LINES</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">全力で行きます！ よろしくお願いします！</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="40" customHeight="1">
+      <c r="A256" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">PPV_SUMMIT_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">やった、勝ちました！最高の舞台で最高の結果、夢みたいです！</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="40" customHeight="1">
+      <c r="A257" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">WAR_VICTORY_LINES</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">14 PPV・対抗戦・天頂戦・トーナメント</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">勝ちました！ うちの団体の底力を見せられましたね！</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="40" customHeight="1">
+      <c r="A258" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">ENDING_LINES.fighter.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">ENDING_LINES</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">fighter.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">18 経営危機・エンディング</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">最後まで楽しかったです！ ありがとうございました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="40" customHeight="1">
+      <c r="A259" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES.polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">FA_GREETING_LINES</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">polite.easygoing[1]</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">19 ドラフト・スカウト</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">フリー生活は今日で卒業です！　ここから楽しくなりそう！</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="40" customHeight="1">
+      <c r="A260" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES.polite.easygoing[1]</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr" s="2">
+      <c r="B260" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">SCOUT_GREETING_LINES</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr" s="12">
+      <c r="D260" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">polite.easygoing[1]</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr" s="2">
+      <c r="E260" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">19 ドラフト・スカウト</t>
         </is>
       </c>
-      <c r="F253" t="inlineStr" s="3">
+      <c r="F260" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">声をかけてくださって嬉しいです！　思いきり暴れますね！</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H253"/>
+  <autoFilter ref="A1:H260"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/キャラタイプ別/丁寧×お気楽.xlsx
+++ b/セリフ編集/キャラタイプ別/丁寧×お気楽.xlsx
@@ -2309,7 +2309,7 @@
       </c>
       <c r="F62" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">社長、あの方とやってみたいのですけれど、だめでしょうか。</t>
+          <t xml:space="preserve">社長、三人で挑んでみたいのですけれど、だめでしょうか。</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="F63" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">あの方と一度、やってみたいんです。だめならいいので。</t>
+          <t xml:space="preserve">一度、三人で乗り込んでみたいんです。だめならいいので。</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="F64" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ふと思ったんです。あの方とやってみたいなって。</t>
+          <t xml:space="preserve">ふと思ったんです。三人であちらへ行ってみたいなって。</t>
         </is>
       </c>
     </row>
